--- a/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_7.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_7.xlsx
@@ -575,46 +575,46 @@
         <v>33</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.008589835360112</v>
+        <v>-3.995526897219257</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.652609627448165</v>
+        <v>-8.624748692782362</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04552372346606859</v>
+        <v>0.04584990788012533</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1758679677562611</v>
+        <v>0.175690606739721</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.42962840351089</v>
+        <v>-6.408736863605171</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.06544722024159455</v>
+        <v>-0.06468026918098246</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.185111029965526</v>
+        <v>-3.17444660275806</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.488208479395922</v>
+        <v>8.461523669842123</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.429094267574847</v>
+        <v>8.402680838380341</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.579078864480159</v>
+        <v>7.555441686846457</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.45111327054897</v>
+        <v>13.40880363996503</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.411683826594057</v>
+        <v>7.388828255972754</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.03126240517386</v>
+        <v>9.999987126282456</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.28390157018622</v>
+        <v>10.25211424924069</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.485028652972126</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.60544437807566</v>
+        <v>-1.599822594357015</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.001536000565814</v>
+        <v>2.992327838372034</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.132616310305437</v>
+        <v>3.122893101272268</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.096852969973895</v>
+        <v>5.080922470294524</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.113449318854883</v>
+        <v>-2.106058729584646</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.198882688891686</v>
+        <v>-2.191207950176498</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.845775301330661</v>
+        <v>4.830362497791889</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.729136119181838</v>
+        <v>-2.720016078989282</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.08752430563284</v>
+        <v>-6.067482156738443</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.224379051804775</v>
+        <v>1.220763299525927</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.258868054563351</v>
+        <v>1.255455917004753</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.852670308385321</v>
+        <v>5.834314245458025</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.12051106983745</v>
+        <v>11.0854475825754</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>46</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.028300810223811</v>
+        <v>4.015600638857165</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2428365282288283</v>
+        <v>0.2425456604218894</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1521913086470406</v>
+        <v>-0.151302395735236</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.02188571367939574</v>
+        <v>-0.0215204419654853</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.615200572516997</v>
+        <v>1.61029253848173</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.08993074113183</v>
+        <v>4.07722882660984</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.53762323309537</v>
+        <v>10.50388296692628</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.894792701622649</v>
+        <v>7.869092924876043</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.657156290243705</v>
+        <v>5.639094643378961</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.627525701366771</v>
+        <v>2.619548758023726</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2437155103423123</v>
+        <v>0.2432232315299814</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.457894812342637</v>
+        <v>2.450494530215309</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.037190244284261</v>
+        <v>2.030894105872818</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.073981513139344</v>
+        <v>-2.066726330467098</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.125017267577597</v>
+        <v>-5.201961067477164</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-20.77701101341271</v>
+        <v>-21.08562444889345</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-13.19409612408126</v>
+        <v>-13.39046313942486</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.804160846449008</v>
+        <v>-7.920581063550443</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.09122846000276</v>
+        <v>-10.24141878229829</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-11.55649049430571</v>
+        <v>-11.72916858372557</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-11.64398726961699</v>
+        <v>-11.81690919969436</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-17.38031568030724</v>
+        <v>-17.63558691722751</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-17.44273421465967</v>
+        <v>-17.7008280896351</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-18.28264212769692</v>
+        <v>-18.55452254905394</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-16.73154535642641</v>
+        <v>-16.97960026307518</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-20.21860148034666</v>
+        <v>-20.51916142994698</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-13.6017470716209</v>
+        <v>-13.80358120250574</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-16.87741114143997</v>
+        <v>-17.12883813170951</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>51</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4477381503787043</v>
+        <v>0.4468746828876959</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.68090846465217</v>
+        <v>6.661628396606083</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.48176954486857</v>
+        <v>-5.463808566036981</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.391092368770778</v>
+        <v>-3.379950257954924</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.9685844115401</v>
+        <v>-1.961735771968755</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2913198863203874</v>
+        <v>0.2914222267418012</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.169877800571683</v>
+        <v>2.163942110193041</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.666400202936153</v>
+        <v>3.655610819446935</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.641618372360142</v>
+        <v>1.637509124799344</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.754694118274195</v>
+        <v>2.747473600834653</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.480972808267126</v>
+        <v>6.461936721397237</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.584993059158698</v>
+        <v>2.578413715779078</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1982245608814424</v>
+        <v>0.198493783561922</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.415152061174993</v>
+        <v>2.40897699433922</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>62</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.958174583015456</v>
+        <v>3.946234827744497</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7337919395236625</v>
+        <v>0.7326615961914982</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.501164514849314</v>
+        <v>-4.485758013914698</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.758304349943678</v>
+        <v>-2.748823938421395</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.297954609276502</v>
+        <v>-3.286718157888139</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-7.844985932528509</v>
+        <v>-7.819267843342651</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.931850341059096</v>
+        <v>-7.906162210690326</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-5.170878966134914</v>
+        <v>-5.154168835013039</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.229801011329101</v>
+        <v>1.226866334427925</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.23836289583803</v>
+        <v>-1.233227493627709</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.443702218502963</v>
+        <v>-1.43835608540941</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.410144571688292</v>
+        <v>-1.404342439265719</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.638608006477327</v>
+        <v>4.624907087714327</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.271922125793935</v>
+        <v>3.262866937414842</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.006561679790018</v>
+        <v>5.053989941126467</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>12.14814435431754</v>
+        <v>12.2620903280822</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.751801898911992</v>
+        <v>6.812543675138542</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.131888891758202</v>
+        <v>3.159260852046707</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.414273658011155</v>
+        <v>-7.48918301173525</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.364703648587096</v>
+        <v>-3.401679143272602</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.450447122283919</v>
+        <v>-3.487318215050628</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.340879912204329</v>
+        <v>2.361360237189096</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.532572483605215</v>
+        <v>3.5640129231546</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.145130624403052</v>
+        <v>7.210190430707968</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.932142166366212</v>
+        <v>1.948102702541419</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.221470630613254</v>
+        <v>3.24815474244825</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.057016823878946</v>
+        <v>4.094177544723742</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.052958084845045</v>
+        <v>3.079118468650776</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4101049868766395</v>
+        <v>-0.4132706656039176</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-5.148126482931481</v>
+        <v>-5.188911063462903</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-9.710977708569473</v>
+        <v>-9.788827772824206</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-12.13749814967324</v>
+        <v>-12.23340039546908</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-12.67150389139952</v>
+        <v>-12.77351020870247</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-14.4651722307334</v>
+        <v>-14.58141561960172</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-14.55414945662668</v>
+        <v>-14.67033249379196</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-9.808122804152084</v>
+        <v>-9.885488712804722</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8.827647698231353</v>
+        <v>-8.89768422807218</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-9.669758018320195</v>
+        <v>-9.746803626127146</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.744724468398317</v>
+        <v>-6.798888746254491</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.711258676881826</v>
+        <v>-6.76638003274207</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.043781462986253</v>
+        <v>-5.083887596230532</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-5.84073634422284</v>
+        <v>-5.888236627950917</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.473030156944667</v>
+        <v>-1.484502363412481</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.080025202689221</v>
+        <v>5.117364358975493</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.643553176384877</v>
+        <v>2.659343323607558</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.856639610782246</v>
+        <v>6.90530525307468</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.256580852553</v>
+        <v>3.275258675112511</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.597427635599118</v>
+        <v>5.633505310890421</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.6153518875723449</v>
+        <v>-0.6266059266496811</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.214160115285296</v>
+        <v>-7.273412946230131</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.166739342214754</v>
+        <v>-2.187001816777169</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.04796911097595569</v>
+        <v>0.04417725189441057</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.621579485439256</v>
+        <v>-1.637468265297684</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.67646447827557</v>
+        <v>-5.724975352499477</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-7.120432256798729</v>
+        <v>-7.177627307669248</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.873319886436988</v>
+        <v>-6.930016334950615</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>109</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.704447494521901</v>
+        <v>-5.689342982089862</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.565094350223717</v>
+        <v>-4.552792963749397</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.134484799681545</v>
+        <v>5.122443551029612</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.182519228994529</v>
+        <v>6.167327043938094</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7805164082385829</v>
+        <v>-0.776430169849462</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4832949776558451</v>
+        <v>-0.4799092973295487</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.268416420231858</v>
+        <v>1.267394538338799</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.036548700224245</v>
+        <v>-1.032111400302938</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.578235940287385</v>
+        <v>2.57284405614466</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.483690229619278</v>
+        <v>4.473369500909406</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.035806698399725</v>
+        <v>7.018621647014676</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.232991111054417</v>
+        <v>5.221264957628343</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.733316303926202</v>
+        <v>5.719513732127602</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.984756392971413</v>
+        <v>5.970768683492835</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>111</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.362417535645676</v>
+        <v>3.353929886372384</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.751290147151714</v>
+        <v>1.74727412692004</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4460818654120047</v>
+        <v>-0.4437843481555248</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.992475521382964</v>
+        <v>5.976791507711255</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.356546304546875</v>
+        <v>6.341544359702226</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>10.26277084460065</v>
+        <v>10.23723255183259</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>11.98472945138177</v>
+        <v>11.95457205674121</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.61817612215422</v>
+        <v>10.59129445962279</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>11.46304236633471</v>
+        <v>11.43319313669877</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>10.61143530465817</v>
+        <v>10.58380888999486</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>8.601510196507675</v>
+        <v>8.578938754891325</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>10.44336494359639</v>
+        <v>10.41672826628637</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.316590077094311</v>
+        <v>7.297577731409653</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.761920471936953</v>
+        <v>5.747609744737773</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>130</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.891177064405582</v>
+        <v>2.883378135573743</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.896768362284618</v>
+        <v>5.880745703153195</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.73223832943053</v>
+        <v>4.72009068354491</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.554245331540528</v>
+        <v>2.547082090897291</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.864459119643094</v>
+        <v>5.849712292727297</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>6.933878465201673</v>
+        <v>6.915807331422663</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.770307803799703</v>
+        <v>3.761060654679405</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>10.23755775609072</v>
+        <v>10.20971846640273</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>8.638718326244408</v>
+        <v>8.614585925974694</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.245636557814997</v>
+        <v>6.228246724955198</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.811336739037159</v>
+        <v>6.792112801713998</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>9.160062023131189</v>
+        <v>9.135034595209987</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.97093029837432</v>
+        <v>7.948633436597312</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.680356043346713</v>
+        <v>6.662370659498649</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>156</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.057540884312544</v>
+        <v>-5.04248098468392</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.541414369862608</v>
+        <v>-1.536869362741577</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.783923257399614</v>
+        <v>-5.766001237203632</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.729803449492053</v>
+        <v>-3.71898919930257</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.553019491947545</v>
+        <v>-5.535266412858689</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.615442301783041</v>
+        <v>-4.600935749993852</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.776402886165975</v>
+        <v>-2.767089444401556</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.455177618711609</v>
+        <v>-6.436093233755138</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5473007700937984</v>
+        <v>0.5449100886655316</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.622196210035575</v>
+        <v>1.61688997576799</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.344145975211639</v>
+        <v>3.333400491318692</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4.664339380873969</v>
+        <v>4.650296009481444</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.674134289965004</v>
+        <v>1.668425245340686</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.85314762389072</v>
+        <v>3.841857838985362</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>166</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.300667235872623</v>
+        <v>-4.286292114735083</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.093369147695782</v>
+        <v>-1.089720482063086</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.332410452044435</v>
+        <v>3.323718336552396</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.960708266467513</v>
+        <v>-1.954234444779622</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.89783818041662</v>
+        <v>-1.889568751131364</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.203822651127275</v>
+        <v>-2.195259388654478</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.726630970692888</v>
+        <v>0.7259903383244222</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.87985745692049</v>
+        <v>3.868631254394629</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1992070749415689</v>
+        <v>0.19764090287714</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6527899989377275</v>
+        <v>-0.651548337724762</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.875910498248771</v>
+        <v>-3.865190363702233</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.635240210985529</v>
+        <v>-2.627938763557658</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5671969251163205</v>
+        <v>0.5643225364289748</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3912262799129351</v>
+        <v>-0.3904560318822945</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>206</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.81724129144051</v>
+        <v>3.806160160065929</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.720826650267547</v>
+        <v>1.715463865311214</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.268186363160801</v>
+        <v>3.258495958133871</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.943256389534035</v>
+        <v>-1.935936254021001</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.83202888040978</v>
+        <v>3.82206801802085</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.187208400490846</v>
+        <v>2.182112360022238</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.561674450202048</v>
+        <v>3.551351973263849</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.609186902608023</v>
+        <v>2.600689981152925</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.036493425493106</v>
+        <v>3.025108383818662</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.103440011328068</v>
+        <v>5.085379352194131</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.898291453005463</v>
+        <v>4.880823644879179</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.447758886957772</v>
+        <v>4.432116404521281</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.02866064765265</v>
+        <v>4.013672557426062</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.767071045022632</v>
+        <v>4.750496126264714</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.424929026728805</v>
+        <v>3.427350822997198</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.405768832209162</v>
+        <v>1.406844205596798</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6226629500739449</v>
+        <v>-0.6232845298840815</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3242237182342933</v>
+        <v>0.3241746274214208</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6021073757823316</v>
+        <v>0.6020626369610866</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.552011380444497</v>
+        <v>-1.553645579901939</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.4069195784054216</v>
+        <v>0.4070217967059406</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.802662408377998</v>
+        <v>2.80490109620132</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5294983811656522</v>
+        <v>-0.5294524290964446</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.836673489461575</v>
+        <v>-3.8391357346609</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.269435625068645</v>
+        <v>-5.272991553323983</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.19049607892147</v>
+        <v>-3.19254768936203</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.02207085211522</v>
+        <v>-4.024601865814915</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.543358600303726</v>
+        <v>-3.545699958408214</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.32335557291988</v>
+        <v>1.335849103051508</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.372276047722437</v>
+        <v>-2.392997240139664</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8557437031985913</v>
+        <v>-0.8660831300075102</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.015566906468948</v>
+        <v>-3.047052373647965</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.483819910740507</v>
+        <v>-4.531371481145875</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.571949295834521</v>
+        <v>-4.621359763701989</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.741076195540209</v>
+        <v>-6.805732770828456</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-7.977528213463586</v>
+        <v>-8.04758288122445</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.221380439610336</v>
+        <v>-4.25486516980169</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.29579413618697</v>
+        <v>-4.332465307057511</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.11499103365788</v>
+        <v>-4.151168489351903</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.70101468872808</v>
+        <v>-3.732751731972066</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.120375964687533</v>
+        <v>-4.154621240048385</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.575627690501527</v>
+        <v>-1.588297591169685</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>284</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.492477172747726</v>
+        <v>3.482614149787622</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-5.865575313455842</v>
+        <v>-5.849496000285093</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.204105991883495</v>
+        <v>-5.189113041930156</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.904838774768962</v>
+        <v>-1.897578123301791</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.386921961672115</v>
+        <v>-1.379753627014821</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.443130107993959</v>
+        <v>-1.435443068088247</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.175438271970286</v>
+        <v>-1.169315618262353</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.291236029173902</v>
+        <v>-1.286357116123881</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.468280670238819</v>
+        <v>-3.459413563964496</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.96759652008123</v>
+        <v>-3.956557179022276</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.056800645518869</v>
+        <v>-2.050549875362918</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6118560472921288</v>
+        <v>-0.6098063904950521</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.144173265138093</v>
+        <v>2.138543151707559</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.6294828296956609</v>
+        <v>0.627701103702158</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.19714202391372</v>
+        <v>-6.203709116691734</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.302395474233172</v>
+        <v>3.305103368852123</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.169465376718321</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.258516396052215</v>
+        <v>-3.263922142767171</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.426567240754096</v>
+        <v>-3.432752717654623</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.9443718245373987</v>
+        <v>0.9432586824085689</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.230441249546409</v>
+        <v>1.230163083706969</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.090826875662565</v>
+        <v>-1.093119976992675</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.523334585635979</v>
+        <v>-1.525594841944418</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.221588496664026</v>
+        <v>0.2209075404640686</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.129934104027058</v>
+        <v>1.130531560312406</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.804766671399705</v>
+        <v>-1.807270980050873</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.614434301496743</v>
+        <v>-4.619664084273332</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.622243879925989</v>
+        <v>-3.626448328205356</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.657317918872181</v>
+        <v>-1.659213070368395</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.927754408090621</v>
+        <v>-0.929426101425328</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6840658485234883</v>
+        <v>0.6830503867516313</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.205747908501074</v>
+        <v>-5.213221028281744</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.399687518222116</v>
+        <v>-2.404852513195443</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.101304167360659</v>
+        <v>-1.104553954572616</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.524523171178792</v>
+        <v>-2.528709655355243</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.468660232567586</v>
+        <v>-2.47240435202368</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.198199035875525</v>
+        <v>-2.201178780384168</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.381361040190932</v>
+        <v>-3.385795287770812</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5716696307138136</v>
+        <v>-0.5728376870679526</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.549445664296016</v>
+        <v>-2.552743970970752</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.628552667226792</v>
+        <v>-1.63071670272106</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.049535444590504</v>
+        <v>-2.052136310042052</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.545321369712461</v>
+        <v>2.549174802046416</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5461508575234362</v>
+        <v>0.5451634886913226</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.174299244421981</v>
+        <v>-2.182271984208391</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.594433708713751</v>
+        <v>-3.608624646755757</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.032079729987437</v>
+        <v>-1.041388872902424</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8999408578379615</v>
+        <v>-0.9070927779732614</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.311151113413466</v>
+        <v>-3.322419065271241</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.00314071374531</v>
+        <v>-3.012886032765969</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.13073118129946</v>
+        <v>-1.135554743947452</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.200869877880848</v>
+        <v>-1.206885240939691</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.408096996700074</v>
+        <v>-1.412452645590662</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.731885303815716</v>
+        <v>1.732634557742116</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.088315248625115</v>
+        <v>2.090590063528687</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.114418847395108</v>
+        <v>3.118521512536489</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>234</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.211387038158662</v>
+        <v>-1.208146643249563</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.113558941721266</v>
+        <v>-1.107898402243393</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2009740610838833</v>
+        <v>0.2076294586479008</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.886782749246933</v>
+        <v>5.885625465350827</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.921011106824338</v>
+        <v>4.920911621015755</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.936401762488664</v>
+        <v>3.935674906989064</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.569616763165207</v>
+        <v>2.57277594516934</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.102433364383685</v>
+        <v>2.105117450893601</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.757927829076408</v>
+        <v>0.7608365632236911</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.468337842585491</v>
+        <v>5.46128729076996</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.413974070412301</v>
+        <v>1.413836722000291</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.448765743855162</v>
+        <v>1.448288553551635</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.1721666227196152</v>
+        <v>0.1733330879059238</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.005568514644195943</v>
+        <v>-0.004296007168171911</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.360728346456753</v>
+        <v>6.381932201135385</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.790821400159125</v>
+        <v>5.805074999228843</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.312619360229213</v>
+        <v>3.311337093820022</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.922039159503321</v>
+        <v>2.913527883918022</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.466951277764508</v>
+        <v>4.465501759215051</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.681059882146833</v>
+        <v>2.677900675051795</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.67965949820789</v>
+        <v>4.681332019611062</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.212476099426354</v>
+        <v>4.215040632244595</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.450939245049156</v>
+        <v>4.458786578226395</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.206916910083159</v>
+        <v>6.2228162490279</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.917539463502045</v>
+        <v>3.926819504811228</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.998835938678191</v>
+        <v>5.01252536386184</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.9268198101180971</v>
+        <v>0.9273492869483491</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3898360288215557</v>
+        <v>-0.3936100090476771</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>155</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.635593937854516</v>
+        <v>3.624763854076463</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.8469474170452</v>
+        <v>-1.841633474113202</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.145280650551726</v>
+        <v>6.140148458553689</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.856178944449653</v>
+        <v>8.850026675334654</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.027435148732252</v>
+        <v>7.02302541669674</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.615199667093066</v>
+        <v>8.60482168876328</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.949820788530467</v>
+        <v>5.945745023836125</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.418121260716752</v>
+        <v>7.409142764578526</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.131314922921469</v>
+        <v>4.125812413395444</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.636028447570993</v>
+        <v>2.631221135367433</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.439692618682066</v>
+        <v>-1.435398752866959</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.470983312811299</v>
+        <v>2.465658280598845</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.477692374770704</v>
+        <v>-2.470725362604078</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.9348434127608769</v>
+        <v>-0.9306814496826661</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>113</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-6.47573920516578</v>
+        <v>-6.465854143281497</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.892622552643253</v>
+        <v>-1.88308501246587</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.252331749609709</v>
+        <v>1.257307377857245</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.267540634429551</v>
+        <v>2.275583279645673</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.695659341704491</v>
+        <v>-2.675525147576451</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2566498526483088</v>
+        <v>0.2622984594393074</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.056871887588422</v>
+        <v>1.063717513591982</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.474644241019234</v>
+        <v>1.475830227796628</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.241222901800107</v>
+        <v>-1.235524649050987</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.206392334615671</v>
+        <v>-1.203860390751387</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3587658454915044</v>
+        <v>0.3611984974395952</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.284120147801801</v>
+        <v>1.27810475504932</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.292624991003002</v>
+        <v>5.282628905166341</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.431105356070617</v>
+        <v>6.417305989655041</v>
       </c>
     </row>
     <row r="31">
@@ -1872,49 +1872,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.646748595677906</v>
+        <v>2.689819107679853</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.64265161822761</v>
+        <v>6.681693770577631</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.6403062761170233</v>
+        <v>0.6128931620075377</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.443456604986203</v>
+        <v>5.438440157117753</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.2321381936523323</v>
+        <v>0.1721941751836908</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.39873900987272</v>
+        <v>2.39438128748192</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4448464140957356</v>
+        <v>0.4093005738964521</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.826075302442739</v>
+        <v>-2.871806051950699</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.952495749372765</v>
+        <v>-1.983987894324798</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9334620558960154</v>
+        <v>-0.9418988091293272</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.072794819465912</v>
+        <v>-2.106313812041577</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.330420603917986</v>
+        <v>-4.357226685925802</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.9881176453081437</v>
+        <v>-1.003896391210382</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.615635129051611</v>
+        <v>-2.640967511764202</v>
       </c>
     </row>
     <row r="32">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.01593</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4088~4101</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4088</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.07910496191634309</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.01495</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4055~4068</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4055</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.1122647279709525</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.01397</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4015~4028</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4015</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.1381406271584424</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.01299</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3969~3982</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3969</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.09320155924758922</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.01201</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3913~3925</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3913</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.1689820619556315</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.01103</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3862~3874</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3862</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.1653123251178457</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.01005</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3800~3812</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3800</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.1036235895486826</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.009076</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3721~3732</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3721</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.001476905418975605</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.008097</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3626~3636</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3626</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.009311954817526669</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.007118</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3529~3538</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3529</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.05037174197205019</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.006139</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3420~3429</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3420</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.2333041703120387</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.00516</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3309~3318</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3309</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.1286231626110066</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.004181</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3179~3188</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3179</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.01597196837220594</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.003202</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3023~3032</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3023</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.2770102286026912</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.002223</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2857~2866</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2857</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.5421513518067727</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; -0.001244</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2651~2660</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2651</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.2885165670080667</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; -0.000265</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2407~2415</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2407</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.0296702042679442</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.0007139</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2148~2153</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2148</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.1943208097594464</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.001693</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1864~1869</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1864</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.7545405138964441</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.002672</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1595~1599</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1595</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.164472874286588</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.003651</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1297~1300</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1297</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.583484756713105</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.00463</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1040~1042</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1040</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.09773250512592568</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.005609</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>806~808</t>
-        </is>
+      <c r="B28" t="n">
+        <v>806</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.4768587094930012</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.006588</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>615~616</t>
-        </is>
+      <c r="B29" t="n">
+        <v>615</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-1.357074683846342</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.007567</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>460~461</t>
-        </is>
+      <c r="B30" t="n">
+        <v>460</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-3.035737669450761</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.008546</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>347~348</t>
-        </is>
+      <c r="B31" t="n">
+        <v>347</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-1.918725676531807</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.009525</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>241~241</t>
-        </is>
+      <c r="B32" t="n">
+        <v>241</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-3.945720477886326</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.0105</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>171~171</t>
-        </is>
+      <c r="B33" t="n">
+        <v>171</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-5.709812589215829</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.01148</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>112~112</t>
-        </is>
+      <c r="B34" t="n">
+        <v>112</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1851331083614554</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.01246</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>2.268466441694791</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.01593</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-4.874390701162362</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.01495</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>117~117</t>
-        </is>
+      <c r="B7" t="n">
+        <v>117</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-4.630190456962112</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.01397</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>157~157</t>
-        </is>
+      <c r="B8" t="n">
+        <v>157</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-4.085795008108065</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.01299</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>203~203</t>
-        </is>
+      <c r="B9" t="n">
+        <v>203</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-2.247132901490758</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.01201</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>259~260</t>
-        </is>
+      <c r="B10" t="n">
+        <v>259</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-2.878053704825362</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.01103</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>310~311</t>
-        </is>
+      <c r="B11" t="n">
+        <v>310</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-2.332666616029911</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.01005</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>372~373</t>
-        </is>
+      <c r="B12" t="n">
+        <v>372</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.28700400385609</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.009076</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>451~453</t>
-        </is>
+      <c r="B13" t="n">
+        <v>451</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.1755575255079904</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.008097</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>546~549</t>
-        </is>
+      <c r="B14" t="n">
+        <v>546</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.2165712892445839</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.007118</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>643~647</t>
-        </is>
+      <c r="B15" t="n">
+        <v>643</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.4068849971806117</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.006139</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>752~756</t>
-        </is>
+      <c r="B16" t="n">
+        <v>752</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.170686997458652</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.00516</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>863~867</t>
-        </is>
+      <c r="B17" t="n">
+        <v>863</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.5903241333587701</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.004181</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>993~997</t>
-        </is>
+      <c r="B18" t="n">
+        <v>993</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.1363671065690468</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.003202</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1149~1153</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1149</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.802198077365226</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.002223</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1315~1319</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1315</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.242490632567822</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; -0.001244</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1521~1525</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1521</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.5590120907017706</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; -0.000265</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1765~1770</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1765</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.007562613995283129</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.0007139</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2024~2032</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2024</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.1640419947506473</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.001693</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2308~2316</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2308</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.5721920770266422</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.002672</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2577~2586</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2577</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.1345829451133085</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.003651</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2875~2885</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2875</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.292398458858159</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.00463</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3132~3143</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3132</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.05945804658605169</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.005609</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3366~3377</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3366</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.1392778227270028</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.006588</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3557~3569</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3557</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.2104002900449942</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.007567</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3712~3724</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3712</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.3529633983721965</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.008546</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3825~3837</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3825</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.1518574838035747</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.009525</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3931~3944</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3931</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.2195434242119276</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.0105</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4001~4014</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4001</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.2220574446131423</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.01148</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4060~4073</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4060</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.02596962391731239</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.01246</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4088~4101</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4088</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.0672008171619396</v>

--- a/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_7.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_7.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Adr Act MA Ratio-7 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Adr Act MA Ratio-7 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>33</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.995526897219257</v>
+        <v>-3.983048764606934</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.624748692782362</v>
+        <v>-8.611884170228578</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04584990788012533</v>
+        <v>0.05882092147720641</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.175690606739721</v>
+        <v>0.188637088435172</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.408736863605171</v>
+        <v>-6.395659340619275</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.06468026918098246</v>
+        <v>-0.05166381189070535</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.17444660275806</v>
+        <v>-3.161404831769708</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.461523669842123</v>
+        <v>8.474687763771982</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.402680838380341</v>
+        <v>8.415865421854839</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.555441686846457</v>
+        <v>7.568835064525025</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.40880363996503</v>
+        <v>13.42225313592124</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.388828255972754</v>
+        <v>7.402274604042972</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.999987126282456</v>
+        <v>10.01354033597107</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.25211424924069</v>
+        <v>10.24168461354116</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.485028652972126</v>
+        <v>-2.472550165484463</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.599822594357015</v>
+        <v>-1.586953796110556</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.992327838372034</v>
+        <v>3.005300200597311</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.122893101272268</v>
+        <v>3.135840814644318</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.080922470294524</v>
+        <v>5.094005723128184</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.106058729584646</v>
+        <v>-2.093043764869606</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.191207950176498</v>
+        <v>-2.178166223295115</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.830362497791889</v>
+        <v>4.843524991202912</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.720016078989282</v>
+        <v>-2.706835151338872</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.067482156738443</v>
+        <v>-6.054092335663178</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.220763299525927</v>
+        <v>1.23421043205893</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.255455917004753</v>
+        <v>1.268901412669145</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.834314245458025</v>
+        <v>5.847867156203868</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.0854475825754</v>
+        <v>11.07501794687725</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>46</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.015600638857165</v>
+        <v>4.028083480567304</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2425456604218894</v>
+        <v>0.2554149435664925</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.151302395735236</v>
+        <v>-0.1383329307312806</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.0215204419654853</v>
+        <v>-0.008575357555493213</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.61029253848173</v>
+        <v>1.623373278029398</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.07722882660984</v>
+        <v>4.09024629572189</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.50388296692628</v>
+        <v>10.51692977075724</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.869092924876043</v>
+        <v>7.882256211912733</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.639094643378961</v>
+        <v>5.652277815740732</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.619548758023726</v>
+        <v>2.632940417271037</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2432232315299814</v>
+        <v>0.2566699626880435</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.450494530215309</v>
+        <v>2.463940033269587</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.030894105872818</v>
+        <v>2.04444671509367</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.066726330467098</v>
+        <v>-2.07715596616525</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>56</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.201961067477164</v>
+        <v>-5.189248225713399</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-21.08562444889345</v>
+        <v>-21.07252540232937</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-13.39046313942486</v>
+        <v>-14.35362713789735</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.920581063550443</v>
+        <v>-7.907642010728338</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.24141878229829</v>
+        <v>-10.22834575044421</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-11.72916858372557</v>
+        <v>-11.7161599635361</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-11.81690919969436</v>
+        <v>-11.8038729646543</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-17.63558691722751</v>
+        <v>-17.62243398888489</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-17.7008280896351</v>
+        <v>-17.68765288621393</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-18.55452254905394</v>
+        <v>-18.54113674857117</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-16.97960026307518</v>
+        <v>-16.96615717724026</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-20.51916142994698</v>
+        <v>-20.50571909406045</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-13.80358120250574</v>
+        <v>-13.79002971323093</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-17.12883813170951</v>
+        <v>-17.13926776740847</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>51</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4468746828876959</v>
+        <v>0.4593556560076948</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.661628396606083</v>
+        <v>6.674503296968538</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.463808566036981</v>
+        <v>-5.452298182854378</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.379950257954924</v>
+        <v>-3.36700942348044</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.961735771968755</v>
+        <v>-1.948658970832994</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2914222267418012</v>
+        <v>0.3044361581087358</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.163942110193041</v>
+        <v>2.176983910832789</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.655610819446935</v>
+        <v>3.668771327788214</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.637509124799344</v>
+        <v>1.650689987367343</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.747473600834653</v>
+        <v>2.760864435000713</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.461936721397237</v>
+        <v>6.475384030335789</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.578413715779078</v>
+        <v>2.59185879515671</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.198493783561922</v>
+        <v>0.2120460594935594</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.40897699433922</v>
+        <v>2.398547358641956</v>
       </c>
     </row>
     <row r="11">
@@ -832,725 +832,725 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.946234827744497</v>
+        <v>3.065477738247871</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7326615961914982</v>
+        <v>-0.1224124270563607</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.485758013914698</v>
+        <v>-5.26559910852572</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.748823938421395</v>
+        <v>-3.552983976441269</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.286718157888139</v>
+        <v>-4.090957708047469</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-7.819267843342651</v>
+        <v>-8.547142514130748</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.906162210690326</v>
+        <v>-7.04982142966935</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-5.154168835013039</v>
+        <v>-4.348610721818389</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.226866334427925</v>
+        <v>1.930382114342798</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.233227493627709</v>
+        <v>-0.5037456235480491</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.43835608540941</v>
+        <v>-0.7086299335457795</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.404342439265719</v>
+        <v>-0.6744290751707425</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.624907087714327</v>
+        <v>5.25273692856338</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.262866937414842</v>
+        <v>3.89247826433828</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.009563</t>
+          <t>X ≈ -0.009561</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.053989941126467</v>
+        <v>5.802316726135004</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>12.2620903280822</v>
+        <v>13.1239977595948</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.812543675138542</v>
+        <v>7.611483406153191</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.159260852046707</v>
+        <v>3.908100941630146</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.48918301173525</v>
+        <v>-6.869661468539626</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.401679143272602</v>
+        <v>-2.733438800519032</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.487318215050628</v>
+        <v>-4.098570519795985</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.361360237189096</v>
+        <v>1.831044923467253</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.5640129231546</v>
+        <v>3.04976845545702</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.210190430707968</v>
+        <v>6.03180066842507</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.948102702541419</v>
+        <v>1.426430078364014</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.24815474244825</v>
+        <v>2.742560295857679</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.094177544723742</v>
+        <v>3.604778518507956</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.079118468650776</v>
+        <v>2.549376921235634</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.008587</t>
+          <t>X ≈ -0.008583</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4132706656039176</v>
+        <v>0.09716289978000248</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-5.188911063462903</v>
+        <v>-4.644942982707875</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-9.788827772824206</v>
+        <v>-9.203687399278415</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-12.23340039546908</v>
+        <v>-12.1896066184622</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-12.77351020870247</v>
+        <v>-12.15868954520274</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-14.58141561960172</v>
+        <v>-13.94460545846225</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-14.67033249379196</v>
+        <v>-14.03332316176795</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-9.885488712804722</v>
+        <v>-10.3431701205128</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8.89768422807218</v>
+        <v>-9.366426392088712</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-9.746803626127146</v>
+        <v>-10.21821748796371</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.798888746254491</v>
+        <v>-7.300368846973996</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.76638003274207</v>
+        <v>-7.268002910458073</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.083887596230532</v>
+        <v>-5.607468324177681</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-5.888236627950917</v>
+        <v>-6.424982053123223</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.007607</t>
+          <t>X ≈ -0.007605</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.484502363412481</v>
+        <v>-3.008716902224357</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.117364358975493</v>
+        <v>4.527433935455718</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.659343323607558</v>
+        <v>3.109269783938394</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.90530525307468</v>
+        <v>7.314399626896837</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.275258675112511</v>
+        <v>3.714400726515336</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.633505310890421</v>
+        <v>6.051681825349952</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.6266059266496811</v>
+        <v>-1.164217311690528</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.273412946230131</v>
+        <v>-6.728998761376168</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.187001816777169</v>
+        <v>-1.694967564729616</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.04417725189441057</v>
+        <v>0.5048202406694031</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.637468265297684</v>
+        <v>-1.740337204178132</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.724975352499477</v>
+        <v>-5.206863891304337</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-7.177627307669248</v>
+        <v>-6.648752810937509</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.930016334950615</v>
+        <v>-6.424982053122285</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.006629</t>
+          <t>X ≈ -0.006625</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.689342982089862</v>
+        <v>-4.804520305864877</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.552792963749397</v>
+        <v>-4.54847066358132</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.122443551029612</v>
+        <v>4.383754554900108</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.167327043938094</v>
+        <v>5.446073065951389</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.776430169849462</v>
+        <v>-1.619065144703121</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4799092973295487</v>
+        <v>-1.322849858343858</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.267394538338799</v>
+        <v>1.391743536576961</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.032111400302938</v>
+        <v>-0.941868588910495</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.57284405614466</v>
+        <v>2.731664725025681</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.473369500909406</v>
+        <v>4.685013181785877</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.018621647014676</v>
+        <v>7.282494924830701</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.221264957628343</v>
+        <v>5.448938731414763</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.719513732127602</v>
+        <v>5.96450035553103</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.970768683492835</v>
+        <v>6.191840376784008</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.00565</t>
+          <t>X ≈ -0.005647</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.353929886372384</v>
+        <v>3.759485516289452</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.74727412692004</v>
+        <v>2.153339231078249</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4437843481555248</v>
+        <v>-0.021666286944658</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.976791507711255</v>
+        <v>6.344687865177768</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.341544359702226</v>
+        <v>6.6997722906764</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>10.23723255183259</v>
+        <v>10.56338492711569</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>11.95457205674121</v>
+        <v>12.26478385714118</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.59129445962279</v>
+        <v>10.90974953288438</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>11.43319313669877</v>
+        <v>11.74372661044873</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>10.58380888999486</v>
+        <v>10.89772103678474</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>8.578938754891325</v>
+        <v>8.908419541807717</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>10.41672826628637</v>
+        <v>10.72760979148146</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.297577731409653</v>
+        <v>7.632781864175328</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.747609744737773</v>
+        <v>6.075017946877047</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.00467</t>
+          <t>X ≈ -0.004667</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>130</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.883378135573743</v>
+        <v>2.128756177092285</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.880745703153195</v>
+        <v>5.893579835982955</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.72009068354491</v>
+        <v>4.734414724864877</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.547082090897291</v>
+        <v>2.560825177649917</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.849712292727297</v>
+        <v>5.862756839190112</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>6.915807331422663</v>
+        <v>6.928793400252097</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.761060654679405</v>
+        <v>3.77407952359215</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>10.20971846640273</v>
+        <v>9.454597448718069</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>8.614585925974694</v>
+        <v>7.859250662699488</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.228246724955198</v>
+        <v>5.47482738805197</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.792112801713998</v>
+        <v>6.807696443440186</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>9.135034595209987</v>
+        <v>9.148467894709505</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.948633436597312</v>
+        <v>7.19319110972075</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.662370659498649</v>
+        <v>5.882710254569552</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.003691</t>
+          <t>X ≈ -0.003689</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.04248098468392</v>
+        <v>-4.724833737153901</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.536869362741577</v>
+        <v>-1.829274235502716</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.766001237203632</v>
+        <v>-6.08510609103319</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.71898919930257</v>
+        <v>-4.024954336670703</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.535266412858689</v>
+        <v>-5.848194405457988</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.600935749993852</v>
+        <v>-4.909900089688833</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.767089444401556</v>
+        <v>-3.063738432708192</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.436093233755138</v>
+        <v>-6.109020882957218</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5449100886655316</v>
+        <v>0.9175539875566159</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.61688997576799</v>
+        <v>2.002858731275737</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.333400491318692</v>
+        <v>3.087668885140864</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4.650296009481444</v>
+        <v>4.411620682712119</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.668425245340686</v>
+        <v>2.058201176144443</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.841857838985362</v>
+        <v>4.220179237199972</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002713</t>
+          <t>X ≈ -0.002711</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>166</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.286292114735083</v>
+        <v>-4.273829456726638</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.089720482063086</v>
+        <v>-1.076861677846118</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.323718336552396</v>
+        <v>3.337691258580165</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.954234444779622</v>
+        <v>-1.941974615902076</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.889568751131364</v>
+        <v>-1.876505045833163</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.195259388654478</v>
+        <v>-2.182256605663106</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7259903383244222</v>
+        <v>0.739024880110108</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.868631254394629</v>
+        <v>3.881788405090816</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.19764090287714</v>
+        <v>0.2108207980611709</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.651548337724762</v>
+        <v>-0.6382811724291599</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.865190363702233</v>
+        <v>-3.852924196052747</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.627938763557658</v>
+        <v>-2.614499968335302</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5643225364289748</v>
+        <v>0.5778721828056561</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3904560318822945</v>
+        <v>-0.4008856675807237</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001734</t>
+          <t>X ≈ -0.001731</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>206</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.806160160065929</v>
+        <v>3.818624048165773</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.715463865311214</v>
+        <v>1.728318547793286</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.258495958133871</v>
+        <v>3.272579801221177</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.935936254021001</v>
+        <v>-1.923770460012882</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.82206801802085</v>
+        <v>3.835130466552684</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.182112360022238</v>
+        <v>2.195112954922116</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.551351973263849</v>
+        <v>3.564384099447715</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.600689981152925</v>
+        <v>2.613843333501158</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.025108383818662</v>
+        <v>3.038286871497505</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.085379352194131</v>
+        <v>5.100791219750853</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.880823644879179</v>
+        <v>4.896221806158934</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.432116404521281</v>
+        <v>4.44555522953646</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.013672557426062</v>
+        <v>4.027221813744532</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.750496126264714</v>
+        <v>4.740066490566562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.0007545</t>
+          <t>X ≈ -0.0007526</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.427350822997198</v>
+        <v>3.425693770631689</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.406844205596798</v>
+        <v>1.41342300243771</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6232845298840815</v>
+        <v>-0.6069891729654699</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3241746274214208</v>
+        <v>0.337413465614901</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6020626369610866</v>
+        <v>0.6153734375054185</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.553645579901939</v>
+        <v>-1.531135021735899</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.4070217967059406</v>
+        <v>0.4194497156018073</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.80490109620132</v>
+        <v>2.805006268793136</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5294524290964446</v>
+        <v>-0.5165470091224762</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.8391357346609</v>
+        <v>-3.812705059326959</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.272991553323983</v>
+        <v>-5.240723008381622</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.19254768936203</v>
+        <v>-3.167160292365089</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.024601865814915</v>
+        <v>-3.996308504997494</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.545699958408214</v>
+        <v>-3.363757563326836</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002244</t>
+          <t>X ≈ 0.0002263</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>259</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.335849103051508</v>
+        <v>1.347927785096736</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.392997240139664</v>
+        <v>-2.587801704105004</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8660831300075102</v>
+        <v>-0.8530759985899081</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.047052373647965</v>
+        <v>-3.034073231249501</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.531371481145875</v>
+        <v>-4.732209802613582</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.621359763701989</v>
+        <v>-4.605773406685643</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.805732770828456</v>
+        <v>-7.004413723545504</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-8.04758288122445</v>
+        <v>-8.030886085036869</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.25486516980169</v>
+        <v>-4.239996595571995</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.332465307057511</v>
+        <v>-4.31906017940468</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.151168489351903</v>
+        <v>-4.137711195641685</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.732751731972066</v>
+        <v>-3.717707664988112</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.154621240048385</v>
+        <v>-4.139334349876044</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.588297591169685</v>
+        <v>-1.598727226867837</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.001203</t>
+          <t>X ≈ 0.001205</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>284</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.482614149787622</v>
+        <v>3.493092260344113</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-5.849496000285093</v>
+        <v>-5.836586190709042</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.189113041930156</v>
+        <v>-5.176105910512554</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.897578123301791</v>
+        <v>-1.884598980903327</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.379753627014821</v>
+        <v>-1.366642822639882</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.435443068088247</v>
+        <v>-1.420936510788096</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.169315618262353</v>
+        <v>-1.156249363961876</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.286357116123881</v>
+        <v>-1.27225783250703</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.459413563964496</v>
+        <v>-3.44448539201197</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.956557179022276</v>
+        <v>-3.943152051369445</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.050549875362918</v>
+        <v>-2.037092581652701</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6098063904950521</v>
+        <v>-0.5959727253035254</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.138543151707559</v>
+        <v>2.150959631050327</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.627701103702158</v>
+        <v>0.6172714680040059</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.002182</t>
+          <t>X ≈ 0.002184</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>269</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.203709116691734</v>
+        <v>-6.18776502562411</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.305103368852123</v>
+        <v>3.318013178428174</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.169465376718321</v>
+        <v>-1.156458245300719</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.263922142767171</v>
+        <v>-3.250943000368707</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.432752717654623</v>
+        <v>-3.419641913279683</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.9432586824085689</v>
+        <v>0.9569156827132872</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.230163083706969</v>
+        <v>1.243229338007446</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.093119976992675</v>
+        <v>-1.07869333656889</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.525594841944418</v>
+        <v>-1.51114848099369</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2209075404640686</v>
+        <v>0.2343126681168997</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.130531560312406</v>
+        <v>1.143988854022624</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.807270980050873</v>
+        <v>-1.792423145707573</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.619664084273332</v>
+        <v>-4.815602043124144</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.626448328205356</v>
+        <v>-3.636877963903508</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>298</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.659213070368395</v>
+        <v>-1.822842979424387</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.929426101425328</v>
+        <v>-0.9165162918492769</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6830503867516313</v>
+        <v>0.6960575181692334</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.213221028281744</v>
+        <v>-5.20024188588328</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.404852513195443</v>
+        <v>-2.391741708820504</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.104553954572616</v>
+        <v>-1.089068645813043</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.528709655355243</v>
+        <v>-2.515643401054767</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.47240435202368</v>
+        <v>-2.647771557151401</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.201178780384168</v>
+        <v>-2.185826549580774</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.385795287770812</v>
+        <v>-3.37239016011798</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5728376870679526</v>
+        <v>-0.5593803933577348</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.552743970970752</v>
+        <v>-2.536873886590314</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.63071670272106</v>
+        <v>-1.617160656369457</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.052136310042052</v>
+        <v>-2.062565945740204</v>
       </c>
     </row>
     <row r="26">
@@ -1615,150 +1615,150 @@
         <v>257</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.549174802046416</v>
+        <v>2.561697091722039</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5451634886913226</v>
+        <v>0.5580732982673737</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.182271984208391</v>
+        <v>-2.169264852790789</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.608624646755757</v>
+        <v>-3.595645504357293</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.041388872902424</v>
+        <v>-1.028278068527484</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9070927779732614</v>
+        <v>-1.116693690065098</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.322419065271241</v>
+        <v>-3.309352810970765</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.012886032765969</v>
+        <v>-2.999705023470732</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.135554743947452</v>
+        <v>-1.120078171551334</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.206885240939691</v>
+        <v>-1.19348011328686</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.412452645590662</v>
+        <v>-1.398995351880444</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.732634557742116</v>
+        <v>1.745677070616949</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.090590063528687</v>
+        <v>2.10414610988029</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.118521512536489</v>
+        <v>3.108091876838337</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.005119</t>
+          <t>X ≈ 0.005121</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.208146643249563</v>
+        <v>-0.9888236986093517</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.107898402243393</v>
+        <v>-0.8954409612050682</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2076294586479008</v>
+        <v>-0.01154788100286197</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.885625465350827</v>
+        <v>5.642828382601628</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.920911621015755</v>
+        <v>4.680061516631888</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.935674906989064</v>
+        <v>4.124675446820603</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.57277594516934</v>
+        <v>2.342769362376671</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.105117450893601</v>
+        <v>1.875225034377635</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.7608365632236911</v>
+        <v>0.5377189918528842</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.46128729076996</v>
+        <v>5.213147146376443</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.413836722000291</v>
+        <v>1.182099338392817</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.448288553551635</v>
+        <v>1.641243084458623</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.1733330879059238</v>
+        <v>0.3705588923954011</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.004296007168171911</v>
+        <v>0.1707626277282799</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.006098</t>
+          <t>X ≈ 0.0061</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>191</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.381932201135385</v>
+        <v>6.394648738659711</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.805074999228843</v>
+        <v>5.818170919847283</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.311337093820022</v>
+        <v>3.846794497160367</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.913527883918022</v>
+        <v>3.448955993853751</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.465501759215051</v>
+        <v>5.001055779225872</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.677900675051795</v>
+        <v>2.691132562841155</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.681332019611062</v>
+        <v>5.216843056610841</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.215040632244595</v>
+        <v>4.750666871971532</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.458786578226395</v>
+        <v>4.69414701118594</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.2228162490279</v>
+        <v>6.759035305489512</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.926819504811228</v>
+        <v>4.463095101207536</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.01252536386184</v>
+        <v>5.019576928602945</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.9273492869483491</v>
+        <v>0.9409053332999306</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3936100090476771</v>
+        <v>-0.4040396447457582</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.624763854076463</v>
+        <v>3.352855333632242</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.841633474113202</v>
+        <v>-2.138223506580026</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.140148458553689</v>
+        <v>5.898011874151344</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.850026675334654</v>
+        <v>8.624590631499785</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.02302541669674</v>
+        <v>6.78935877410769</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.60482168876328</v>
+        <v>8.37944252775241</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.945745023836125</v>
+        <v>5.703669280084569</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.409142764578526</v>
+        <v>7.179721445087161</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.125812413395444</v>
+        <v>3.875501740263616</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.631221135367433</v>
+        <v>2.376935434273584</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.435398752866959</v>
+        <v>-1.71471277161293</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.465658280598845</v>
+        <v>2.205906998320962</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.470725362604078</v>
+        <v>-2.754613807245356</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.9306814496826661</v>
+        <v>-1.230176858317556</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>113</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-6.465854143281497</v>
+        <v>-6.453331853605874</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.88308501246587</v>
+        <v>-1.870175202889818</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.257307377857245</v>
+        <v>1.270314509274847</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.275583279645673</v>
+        <v>2.288562422044137</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.675525147576451</v>
+        <v>-2.662414343201512</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2622984594393074</v>
+        <v>0.2753413557336728</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.063717513591982</v>
+        <v>1.076783767892458</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.475830227796628</v>
+        <v>1.489011237091866</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.235524649050987</v>
+        <v>-1.222325910096224</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.203860390751387</v>
+        <v>-1.190455263098556</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3611984974395952</v>
+        <v>0.374655791149813</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.27810475504932</v>
+        <v>1.28521339356471</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.282628905166341</v>
+        <v>5.296184951517944</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.417305989655041</v>
+        <v>6.406876353956889</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>106</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.689819107679853</v>
+        <v>2.702341397355475</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.681693770577631</v>
+        <v>6.694603580153682</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.6128931620075377</v>
+        <v>0.6259002934251399</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.438440157117753</v>
+        <v>5.451419299516218</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1721941751836908</v>
+        <v>0.1853049795586301</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.39438128748192</v>
+        <v>2.407424183776286</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4093005738964521</v>
+        <v>0.4223668281969282</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.871806051950699</v>
+        <v>-2.858625042655461</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.983987894324798</v>
+        <v>-1.970789155370035</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9418988091293272</v>
+        <v>-0.9284936814764961</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.106313812041577</v>
+        <v>-2.092856518331359</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.357226685925802</v>
+        <v>-4.858847049558754</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.003896391210382</v>
+        <v>-0.9903403448587795</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.640967511764202</v>
+        <v>-2.651397147462355</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>70</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.3637045369329073</v>
+        <v>0.37622682660853</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.609273781111519</v>
+        <v>1.62218359068757</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9.916086778550969</v>
+        <v>9.929065920949434</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>12.23480842062165</v>
+        <v>12.24791922499659</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.532250358337272</v>
+        <v>2.545293254631638</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.733230926779321</v>
+        <v>6.746297181079797</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>10.5517618137121</v>
+        <v>10.56494282300734</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.776476213244152</v>
+        <v>4.789674952198915</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.497779599644737</v>
+        <v>2.511184727297568</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.007311989612887</v>
+        <v>8.020769283323105</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.327409432672589</v>
+        <v>2.340861721392699</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.764297678870577</v>
+        <v>4.77785372522218</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.7283047254325012</v>
+        <v>0.7178750897343491</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>59</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-16.90021798122694</v>
+        <v>-16.88769569155132</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-10.03721532300474</v>
+        <v>-10.02430551342869</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.95750775841492</v>
+        <v>-1.944500626997318</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.522169880044679</v>
+        <v>-3.509190737646215</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.719069921832308</v>
+        <v>2.732180726207247</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-2.068233903163872</v>
+        <v>-2.055191006869507</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.458052366198892</v>
+        <v>-0.444986111898416</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-6.009981527692233</v>
+        <v>-5.996800518396995</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.68115090540001</v>
+        <v>-2.667952166445247</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.921106598902483</v>
+        <v>-6.907701471249652</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.736029414745516</v>
+        <v>-3.722572121035299</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.70164625740005</v>
+        <v>-3.68819396867994</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.121900868344952</v>
+        <v>-4.108344821993349</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.177264281831384</v>
+        <v>-2.187693917529536</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.037845209682942</v>
+        <v>3.050755019258993</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>20.50011936022925</v>
+        <v>20.51312649164685</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>17.05894392140814</v>
+        <v>17.0719230638066</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>16.52052270633591</v>
+        <v>16.53363351071085</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.532250358337265</v>
+        <v>2.54529325463163</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.123911930363519</v>
+        <v>-1.110845676063043</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.73395247200223</v>
+        <v>-8.720771462706992</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.502220400355249</v>
+        <v>-2.488815272702418</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.8644548467557556</v>
+        <v>0.8779121404659733</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.621440536013402</v>
+        <v>7.634996582365005</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.87116186828969</v>
+        <v>7.860732232591538</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Adr Act MA Ratio-7 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Adr Act MA Ratio-7 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,53 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01593</t>
+          <t>X &gt; -0.01592</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.07910496191634309</v>
+        <v>0.07881093192298749</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.06571977414284191</v>
+        <v>0.06542043187609892</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1475943541301206</v>
+        <v>0.1472728331102005</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1203676124072004</v>
+        <v>0.1200532697801506</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1078165450332449</v>
+        <v>0.1075022968783514</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1745494654801689</v>
+        <v>0.1742203441396839</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1520343455827415</v>
+        <v>0.1517101275083661</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1379157672329328</v>
+        <v>0.1375923956569167</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1637227316902212</v>
+        <v>0.1633925877630986</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1824605101321026</v>
+        <v>0.1821211693065692</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2114534848812255</v>
+        <v>0.2111058284983471</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2596483429066012</v>
+        <v>0.2592889309467665</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2445059030259387</v>
+        <v>0.2441478223230789</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3369152929472179</v>
+        <v>0.3370624565373035</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4055</v>
+        <v>4056</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1122647279709525</v>
+        <v>0.1118586069687169</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1364436852176993</v>
+        <v>0.1360198036387885</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1484223607210566</v>
+        <v>0.147992486237392</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1199173882856286</v>
+        <v>0.1194952653384362</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1608489155597823</v>
+        <v>0.1604126356449811</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1764963412493046</v>
+        <v>0.1760581590186305</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1791055838799664</v>
+        <v>0.1786659444847345</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.07017740452365473</v>
+        <v>0.06976099843112848</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.09667325757906298</v>
+        <v>0.09624968748572371</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1224584438357752</v>
+        <v>0.1220221657212122</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1040521149384972</v>
+        <v>0.1036186832456494</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2016303559445376</v>
+        <v>0.2011729232514625</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1651148104568989</v>
+        <v>0.1646631199191404</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2562244013176951</v>
+        <v>0.2564775129522019</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4015</v>
+        <v>4016</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1381406271584424</v>
+        <v>0.1375997302003213</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1537414812782103</v>
+        <v>0.1531808952697489</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1200895539698621</v>
+        <v>0.1195332460545231</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.08999982202922752</v>
+        <v>0.08945198297482904</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1118319934702683</v>
+        <v>0.1112732622636656</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1992366159275889</v>
+        <v>0.1986587757904346</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2027201645430452</v>
+        <v>0.2021403684666083</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.02275339363181672</v>
+        <v>0.02221354830391675</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1247349197117416</v>
+        <v>0.124168859187165</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.184126594277366</v>
+        <v>0.1835372503963555</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.09292672331122276</v>
+        <v>0.09235780925348536</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1911314711519054</v>
+        <v>0.190538177340926</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1086346168329797</v>
+        <v>0.1080575020278545</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1483367482042937</v>
+        <v>0.148723126160121</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3969</v>
+        <v>3970</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.09320155924758922</v>
+        <v>0.09252107717340152</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1527122567278028</v>
+        <v>0.1519963193952876</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1232349381186282</v>
+        <v>0.122521116112992</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0912923219394699</v>
+        <v>0.09058781613966715</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.09446510380774953</v>
+        <v>0.09375270792482127</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1542913799257306</v>
+        <v>0.1535673334939958</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0833315304010469</v>
+        <v>0.08262391695392779</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.06818427793210446</v>
+        <v>-0.0688599938940655</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.06082447695823134</v>
+        <v>0.06011520377117563</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1559004870633771</v>
+        <v>0.1551562565232487</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.09118481366696329</v>
+        <v>0.09045394047313238</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1649458574666198</v>
+        <v>0.1641964933679532</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.08635597322103195</v>
+        <v>0.08562075044069672</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1740089330415131</v>
+        <v>0.1745141685397158</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3913</v>
+        <v>3914</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1689820619556315</v>
+        <v>0.1680905919822067</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.4566598303323914</v>
+        <v>0.4556685770387645</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.3166331216970661</v>
+        <v>0.3296402531146683</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2059524061683078</v>
+        <v>0.2050233987417656</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2423847300847513</v>
+        <v>0.2414373051830339</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3243587854878243</v>
+        <v>0.3233948063181344</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2536390900446222</v>
+        <v>0.2526913225160214</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.183227566637413</v>
+        <v>0.1822897617828545</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3150162847091238</v>
+        <v>0.3140434135410288</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4236704052904585</v>
+        <v>0.4226555943580124</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3354894301498561</v>
+        <v>0.3344933432815012</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.460961704155892</v>
+        <v>0.4599336606893516</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2851386161652343</v>
+        <v>0.2841481970338577</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.421634651320602</v>
+        <v>0.4222330720688632</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3862</v>
+        <v>3863</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1653123251178457</v>
+        <v>0.1642452597882311</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.374719541135093</v>
+        <v>0.3735664360301101</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3929672817370502</v>
+        <v>0.4059744131546523</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2533063771341943</v>
+        <v>0.2521819992940095</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.2714914482630846</v>
+        <v>0.2703513383377967</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.324793732276035</v>
+        <v>0.3236451016996185</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.228412405935984</v>
+        <v>0.2272864760225843</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1373726868100462</v>
+        <v>0.1362606238418138</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2975519825743191</v>
+        <v>0.2963967722608913</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3929832061778811</v>
+        <v>0.3917861532830003</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2545860609490305</v>
+        <v>0.2534202329942161</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.43299949478439</v>
+        <v>0.4317876130947838</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2862828125564292</v>
+        <v>0.2851001020337378</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3953906172724473</v>
+        <v>0.3961414260385183</v>
       </c>
     </row>
     <row r="12">
@@ -2529,930 +2529,930 @@
         <v>3800</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1036235895486826</v>
+        <v>0.1161458792243053</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3688794339210162</v>
+        <v>0.3817892434970673</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4725675365608453</v>
+        <v>0.5000031320667233</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3022885033353688</v>
+        <v>0.315267645733833</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3295464471002916</v>
+        <v>0.3426572514752309</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.4576705264045415</v>
+        <v>0.4707134226989069</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.3611344128388367</v>
+        <v>0.3479332649853788</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2237083642713671</v>
+        <v>0.2106150698356544</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2823894852545976</v>
+        <v>0.2693070152737533</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4195161175957622</v>
+        <v>0.4066331274778321</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2822077486001362</v>
+        <v>0.2693700120710645</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.4629771789715207</v>
+        <v>0.4501275213476035</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2154947322775413</v>
+        <v>0.2027419125412706</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3486054773122333</v>
+        <v>0.3381758416140812</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.009076</t>
+          <t>X &gt; -0.009072</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3721</v>
+        <v>3722</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.001476905418975605</v>
+        <v>-0.003016218051101305</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1163764345555975</v>
+        <v>0.1147574691135063</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3379644419766947</v>
+        <v>0.3509715733942969</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2416325464559819</v>
+        <v>0.2399745245409548</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4955447344553079</v>
+        <v>0.4938020285201432</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5396078077548481</v>
+        <v>0.5378611587040112</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4428403407085639</v>
+        <v>0.4411163104482796</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.178324193897673</v>
+        <v>0.1766565720969879</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2127178239823451</v>
+        <v>0.2110383445767354</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2753443168067591</v>
+        <v>0.2887494444595902</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2468393795161887</v>
+        <v>0.2451221117027629</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4038454865461887</v>
+        <v>0.4020862111886103</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1331469918359218</v>
+        <v>0.1314472174135375</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2906343603233168</v>
+        <v>0.2918368614393074</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.008097</t>
+          <t>X &gt; -0.008094</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3626</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.009311954817526669</v>
+        <v>-0.005668505781876831</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.255373211254927</v>
+        <v>0.2407727044623371</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6032830466115726</v>
+        <v>0.6039355175135981</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5684742810072478</v>
+        <v>0.5690533413441159</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.8431895826626956</v>
+        <v>0.8287825004113216</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.9357736173518987</v>
+        <v>0.9212910525947962</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8388004673708807</v>
+        <v>0.8243336820237843</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4419927615029522</v>
+        <v>0.45517377079819</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.451407342720664</v>
+        <v>0.4646060816754272</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.537921276150044</v>
+        <v>0.5669261751580521</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4314351246756587</v>
+        <v>0.4448924183858765</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5917030222142472</v>
+        <v>0.6051553109343573</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.2698315715012072</v>
+        <v>0.2833876178528101</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.4525187353608402</v>
+        <v>0.4696676986698591</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.007118</t>
+          <t>X &gt; -0.007115</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.05037174197205019</v>
+        <v>0.07774950523041468</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.121733896625031</v>
+        <v>0.1216987813791874</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.546769063367428</v>
+        <v>0.5343428990017998</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3942967224097558</v>
+        <v>0.3816826111898806</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.7763404180359998</v>
+        <v>0.7486264385750943</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8066492267955852</v>
+        <v>0.7787801977960385</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.879079418977561</v>
+        <v>0.8795712096269597</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6540625698481293</v>
+        <v>0.6547341189141491</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5239280818737626</v>
+        <v>0.5245942385200095</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5514925910700725</v>
+        <v>0.5686513400049691</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4883021206596183</v>
+        <v>0.5055932412348696</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7653266556365281</v>
+        <v>0.7666002887743204</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4745364485993946</v>
+        <v>0.4759470742080936</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6554390815836229</v>
+        <v>0.6611857473307623</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006139</t>
+          <t>X &gt; -0.006136</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2333041703120387</v>
+        <v>0.2304542318563136</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2707173550404676</v>
+        <v>0.2677695591081459</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4009361630296482</v>
+        <v>0.4139432944472503</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.210302481168064</v>
+        <v>0.2232816235665283</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.82582930519375</v>
+        <v>0.822681685406657</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.847653577418285</v>
+        <v>0.8445137306832038</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8667032938283299</v>
+        <v>0.863551788702182</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7078032022301315</v>
+        <v>0.7046717072617739</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4586263739218523</v>
+        <v>0.4555628026661367</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4264970989143819</v>
+        <v>0.439902226567213</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2801720538839731</v>
+        <v>0.2936293475941909</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6233099085847442</v>
+        <v>0.6201488963853876</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3073719679255404</v>
+        <v>0.3042793743830288</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4860323778970397</v>
+        <v>0.4882012266200064</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.00516</t>
+          <t>X &gt; -0.005157</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3309</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1286231626110066</v>
+        <v>0.1110068145530505</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2211864388486831</v>
+        <v>0.203948524577882</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4292722091890866</v>
+        <v>0.4286874084139711</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.01686631255328308</v>
+        <v>0.01608987407711737</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.6408053187777796</v>
+        <v>0.6237593077124259</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.532681299944727</v>
+        <v>0.5155582837202388</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4947620932591832</v>
+        <v>0.4776533324721512</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3762626976757133</v>
+        <v>0.3592595838197283</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.09048587507983541</v>
+        <v>0.07349137731961974</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.08577131807123806</v>
+        <v>0.0859355578623493</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.001790940613553005</v>
+        <v>0.002043822737157086</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2947908884261281</v>
+        <v>0.2780408213624952</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.0728863711450316</v>
+        <v>0.05623093713408878</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3095334091090933</v>
+        <v>0.2991037734109412</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004181</t>
+          <t>X &gt; -0.004178</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3179</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.01597196837220594</v>
+        <v>0.02849425804782868</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.01025197082719131</v>
+        <v>-0.02871963222698781</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2538062130688346</v>
+        <v>0.252611739606607</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.08660271896125238</v>
+        <v>-0.08797290964872673</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4277955966596778</v>
+        <v>0.4095190815117036</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2716538120264715</v>
+        <v>0.2532995340665281</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3611921615244711</v>
+        <v>0.3428513806490656</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.02586037559717624</v>
+        <v>-0.01267936630193844</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2580932399300124</v>
+        <v>-0.2448945009752492</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1654151565732747</v>
+        <v>-0.1344343502611594</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2758881540523959</v>
+        <v>-0.2762621982415681</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.06671640376698917</v>
+        <v>-0.08470077018677102</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2491794100782485</v>
+        <v>-0.2356233637266456</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.04974453130140688</v>
+        <v>0.07077132844377587</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003202</t>
+          <t>X &gt; -0.0032</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2770102286026912</v>
+        <v>0.2721337551563821</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.06852815260603506</v>
+        <v>0.06357069962081141</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5644545631325144</v>
+        <v>0.5774616945501165</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1008442843246371</v>
+        <v>0.1138234267231013</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.735515634200155</v>
+        <v>0.7302682847128565</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.523100709702689</v>
+        <v>0.5179476629296502</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5226251521048511</v>
+        <v>0.5174616389395368</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3049356303150503</v>
+        <v>0.2997984561456732</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2995317180183079</v>
+        <v>-0.3044776741638842</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2573898838790072</v>
+        <v>-0.2439847562261761</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4621432081965864</v>
+        <v>-0.4486859144863686</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3101348412353246</v>
+        <v>-0.3151669822235803</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3481361835633194</v>
+        <v>-0.3531970421922566</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.1459450737262813</v>
+        <v>-0.1419132700539762</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.002223</t>
+          <t>X &gt; -0.002221</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5421513518067727</v>
+        <v>0.5361750053917049</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1358257631608453</v>
+        <v>0.1298099489768347</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.404133321834756</v>
+        <v>0.4171404532523582</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.2202503287878201</v>
+        <v>0.2332294711862843</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8880406632393658</v>
+        <v>0.8816763927851667</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6810453286481817</v>
+        <v>0.6747824804896183</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5108090439800748</v>
+        <v>0.5045926753166086</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.09787456150258578</v>
+        <v>0.09174725547215701</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3284188916510189</v>
+        <v>-0.3344075364414891</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2344881326229995</v>
+        <v>-0.2210830049701684</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2644162821154055</v>
+        <v>-0.2509589884051877</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1754636997913153</v>
+        <v>-0.1816158010848312</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4011526860199908</v>
+        <v>-0.4072759404951469</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.131738276717563</v>
+        <v>-0.1268714862928064</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.001244</t>
+          <t>X &gt; -0.001242</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2885165670080667</v>
+        <v>0.2812034734115301</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.01307757415935384</v>
+        <v>0.005642237304073205</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1823307178824294</v>
+        <v>0.1953378493000315</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3878000971992179</v>
+        <v>0.4007792395976821</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.660047590781808</v>
+        <v>0.6522602769495265</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5644026245881832</v>
+        <v>0.5566874285540706</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2745390162801726</v>
+        <v>0.2669165692189495</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.09661052957549288</v>
+        <v>-0.1041621683868073</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5890098455351165</v>
+        <v>-0.5963890779329688</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6478765527936332</v>
+        <v>-0.6344714251408021</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6642350014518357</v>
+        <v>-0.6507777077416179</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.5335027422237602</v>
+        <v>-0.5410416051225369</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7442134178758479</v>
+        <v>-0.751735419142733</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5111197505064595</v>
+        <v>-0.5049217212977126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.000265</t>
+          <t>X &gt; -0.0002631</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2407</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.0296702042679442</v>
+        <v>-0.03886305040190763</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1282099447732392</v>
+        <v>-0.137650777842488</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.263996742167862</v>
+        <v>0.2770038735854641</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3942498747753618</v>
+        <v>0.407229017173826</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.6659255836078515</v>
+        <v>0.6560148576158369</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.7791112917654104</v>
+        <v>0.7691994768802104</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.2611091041805125</v>
+        <v>0.2513907608002413</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.390739668208461</v>
+        <v>-0.4002761140075322</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5950472404711462</v>
+        <v>-0.6045159191704457</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3243754142910973</v>
+        <v>-0.3109702866382662</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.197040735287807</v>
+        <v>-0.1835834415775892</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2639526935732661</v>
+        <v>-0.2737382904675911</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.41167715643126</v>
+        <v>-0.4214818229506108</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.2035013164690582</v>
+        <v>-0.2139309521672104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0007139</t>
+          <t>X &gt; 0.0007157</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2148</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1943208097594464</v>
+        <v>-0.2060785189280452</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.144871949779791</v>
+        <v>0.1577817593558422</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4002587006843541</v>
+        <v>0.4132658321019562</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.809192743649497</v>
+        <v>0.8221718860479612</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.292601533222005</v>
+        <v>1.305712337596944</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.430285408788713</v>
+        <v>1.417299093660276</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.113209684081497</v>
+        <v>1.126275938381973</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5325016689289441</v>
+        <v>0.5198020901342701</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1537563448954486</v>
+        <v>-0.1661595433845946</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.158909167751041</v>
+        <v>0.1723142954038721</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2797372387823032</v>
+        <v>0.2931945324925209</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.154305663477615</v>
+        <v>0.1415261732199298</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.03963686482425288</v>
+        <v>0.02680672661814043</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.03652634666110544</v>
+        <v>-0.04695598235925758</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.001693</t>
+          <t>X &gt; 0.001695</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1864</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7545405138964441</v>
+        <v>-0.7696860840102886</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.058176937879807</v>
+        <v>1.071086747455858</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.25185825803549</v>
+        <v>1.264865389453092</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.221597746983278</v>
+        <v>1.234576889381742</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.699762941755942</v>
+        <v>1.712873746130882</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.866909275437344</v>
+        <v>1.849734132106263</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.460976414696113</v>
+        <v>1.474042668996589</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8096239301709005</v>
+        <v>0.7928412628972197</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3498952914863125</v>
+        <v>0.3333278713204422</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7859437398989115</v>
+        <v>0.7993488675517426</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6347809836413418</v>
+        <v>0.6482382773515596</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2707261695549974</v>
+        <v>0.2538918852267216</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2801535780270683</v>
+        <v>-0.2968303038854785</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1377283830898435</v>
+        <v>-0.1481580187879956</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.002672</t>
+          <t>X &gt; 0.002673</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1595</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.164472874286588</v>
+        <v>0.1440839694656475</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.6792282169195758</v>
+        <v>0.6921380264956269</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.660219422768265</v>
+        <v>1.673226554185867</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.978089816163759</v>
+        <v>1.991068958562224</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.565372165819547</v>
+        <v>2.578482970194486</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.022684829998312</v>
+        <v>2.000309782818945</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.499903553276731</v>
+        <v>1.512969807577207</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.130525567178424</v>
+        <v>1.108479386568938</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6662005240210291</v>
+        <v>0.6444025664756197</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.881238246261276</v>
+        <v>0.8946433739141071</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5511716387356813</v>
+        <v>0.5646289324458991</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.6211846229995004</v>
+        <v>0.5990070848012223</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4517137111141523</v>
+        <v>0.4652697574657552</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4506513443308862</v>
+        <v>0.440221708632734</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.003651</t>
+          <t>X &gt; 0.003652</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1297</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.583484756713105</v>
+        <v>0.5960070463887277</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.048834220671921</v>
+        <v>1.061744030247972</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.884734744844565</v>
+        <v>1.897741876262167</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.630372492836671</v>
+        <v>3.643351635235135</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.707335893149121</v>
+        <v>3.720446697524061</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.741202299390871</v>
+        <v>2.710128419466841</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.425521699901502</v>
+        <v>2.438587954201978</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.958338301120001</v>
+        <v>1.971519310415239</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.325012422797244</v>
+        <v>1.294678801313552</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.861636082145282</v>
+        <v>1.875041209798113</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.8094251307090587</v>
+        <v>0.8228824244192765</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.350429589077471</v>
+        <v>1.319510191566586</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.9301749781325697</v>
+        <v>0.9437310244841726</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.0256943057828</v>
+        <v>1.015264670084647</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.00463</t>
+          <t>X &gt; 0.004631</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1040</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.09773250512592568</v>
+        <v>0.1102547948015484</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.173299007324808</v>
+        <v>1.186208816900859</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.889754676927836</v>
+        <v>2.902761808345439</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.419240055216719</v>
+        <v>5.432219197615183</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.880818840144549</v>
+        <v>4.893929644519488</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.642752140624118</v>
+        <v>3.655795036918484</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.845926292833617</v>
+        <v>3.858992547134093</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.186804314397598</v>
+        <v>3.199985323692836</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.933056424579341</v>
+        <v>1.891402399415739</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.619914909099933</v>
+        <v>2.633320036752764</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.358485311967748</v>
+        <v>1.371942605677965</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.255980861244005</v>
+        <v>1.214197799339722</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.6434185579914171</v>
+        <v>0.65697460434302</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.5085245056523178</v>
+        <v>0.4980948699541656</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.005609</t>
+          <t>X &gt; 0.00561</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4768587094930012</v>
+        <v>0.4311037959836099</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.835582126231714</v>
+        <v>1.793895398087066</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.668436191912342</v>
+        <v>3.753523022006128</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.28383783937133</v>
+        <v>5.370737013178143</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.869179000536782</v>
+        <v>4.956363197381087</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.557710047163333</v>
+        <v>3.518916904835258</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.215550587316798</v>
+        <v>4.301616706659544</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.500842436060047</v>
+        <v>3.586716588275529</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.273378319811627</v>
+        <v>2.28657705876639</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.795000346679608</v>
+        <v>1.880202805993058</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.342415547764752</v>
+        <v>1.427362689916485</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.200149595735333</v>
+        <v>1.089532405547246</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.7798949847904311</v>
+        <v>0.7405866444767994</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.6574078803421415</v>
+        <v>0.5936514872499217</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.006588</t>
+          <t>X &gt; 0.006589</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.357074683846342</v>
+        <v>-1.424005461428656</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.6027802746179702</v>
+        <v>0.5420442178652394</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.77934013944995</v>
+        <v>3.724508605467925</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.019982882447074</v>
+        <v>5.968554887267665</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.994548680361909</v>
+        <v>4.942460456123186</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.830951657038611</v>
+        <v>3.776419851611934</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.070893264441658</v>
+        <v>4.016912744378288</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.279034540984831</v>
+        <v>3.224640848559027</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.594658031425908</v>
+        <v>1.53764243187365</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4198575217226548</v>
+        <v>0.3625203835112671</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.5397795220804014</v>
+        <v>0.4830224772835976</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.01614346287003343</v>
+        <v>-0.133005874426118</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.734100234038948</v>
+        <v>0.6782725246637469</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.9838215663152354</v>
+        <v>0.9040081748902793</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>460</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.035737669450761</v>
+        <v>-3.023215379775138</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.426441429081734</v>
+        <v>1.439351238657785</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.983850379751956</v>
+        <v>2.996857511169559</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.066381169626261</v>
+        <v>5.079360312024725</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.311040214857783</v>
+        <v>4.324151019232723</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.222365015914008</v>
+        <v>2.235407912208373</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.439149736819601</v>
+        <v>3.452215991120077</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.887367639556537</v>
+        <v>1.900548648851775</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.7417690548926856</v>
+        <v>0.7549677938474488</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3252758698315645</v>
+        <v>-0.3118707421787335</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.20532872342136</v>
+        <v>1.218786017131578</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.8092365300603319</v>
+        <v>-0.9160332274762197</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.813987119864322</v>
+        <v>1.827543166215925</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.628925843444961</v>
+        <v>1.618496207746809</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>347</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.918725676531807</v>
+        <v>-1.906203386856184</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.504183469124619</v>
+        <v>2.517093278700671</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.546096371723429</v>
+        <v>3.559103503141031</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.975200079043574</v>
+        <v>5.988179221442039</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.586204151327721</v>
+        <v>6.59931495570266</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.860657583296259</v>
+        <v>2.873700479590624</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.21270547521938</v>
+        <v>4.225771729519856</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.02138414540341</v>
+        <v>2.034565154698647</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.38567161554294</v>
+        <v>1.398870354497703</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.03916621316315627</v>
+        <v>-0.02576108551032519</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.480218393553756</v>
+        <v>1.493675687263973</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.488975911090286</v>
+        <v>-1.632865700610587</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.6844294203279233</v>
+        <v>0.6979854666795262</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.06959743848317856</v>
+        <v>0.05916780278502642</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>241</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.945720477886326</v>
+        <v>-3.933198188210703</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.6667722991909173</v>
+        <v>0.6796821087669684</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.836218945291421</v>
+        <v>4.849226076709023</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.211285355907215</v>
+        <v>6.224264498305679</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.407303974859943</v>
+        <v>9.420414779234882</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.065741763198005</v>
+        <v>3.078784659492371</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.885572361278427</v>
+        <v>5.898638615578903</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.173575684488632</v>
+        <v>4.18675669378387</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.867762520298037</v>
+        <v>2.8809612592528</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3578862979257025</v>
+        <v>0.3712914255785336</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.057697288960824</v>
+        <v>3.071154582671042</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2274216283825439</v>
+        <v>-0.2139693396624338</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.427012557353059</v>
+        <v>1.440568603704662</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.261796130293234</v>
+        <v>1.251366494595082</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>171</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-5.709812589215829</v>
+        <v>-5.697290299540207</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2809529791064733</v>
+        <v>0.2938627886825245</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.734037488884148</v>
+        <v>5.74704462030175</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.694699978216796</v>
+        <v>4.707679120615261</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.249846014606611</v>
+        <v>8.26295681898155</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.53857762686286</v>
+        <v>5.551643881163336</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.562622298256798</v>
+        <v>1.575803307552036</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.086417733711919</v>
+        <v>2.099616472666682</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.031539224366412</v>
+        <v>1.04499651807663</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.27325890483786</v>
+        <v>-1.25980661611775</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.06087244912951917</v>
+        <v>0.07442849548112207</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.480184424680665</v>
+        <v>1.469754788982513</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>112</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1851331083614554</v>
+        <v>0.1976553980370781</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.716416638254337</v>
+        <v>5.729326447830388</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.023229635693816</v>
+        <v>9.036208778092281</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.16337984919308</v>
+        <v>11.17649065356802</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.103678929765877</v>
+        <v>6.116721826060243</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.697516641065029</v>
+        <v>8.710582895365505</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.551761813712098</v>
+        <v>5.564942823007335</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.597904784672657</v>
+        <v>4.61110352362742</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.854922456787591</v>
+        <v>2.868327584440422</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>3.543026275327151</v>
+        <v>3.556483569037368</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>0.01943314996412226</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.264297678870541</v>
+        <v>2.277853725222144</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.406876154003967</v>
+        <v>3.396446518305815</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>6.609273781111476</v>
+        <v>6.622183590687527</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.214405074514886</v>
+        <v>6.227412205932488</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6.344658207122386</v>
+        <v>6.35763734952085</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>9.3776655634788</v>
+        <v>9.390776367853739</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.294155120242074</v>
+        <v>7.307198016536439</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.31366657561687</v>
+        <v>10.32684758491211</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.435883418184289</v>
+        <v>4.449340711894507</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2916381863750317</v>
+        <v>-0.2781858976549216</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.918780915908734</v>
+        <v>1.908351280210582</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Adr Act MA Ratio-7 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Adr Act MA Ratio-7 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,53 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01593</t>
+          <t>X &lt; -0.01592</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.874390701162362</v>
+        <v>-4.861868411486739</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-8.071309211199392</v>
+        <v>-8.058302079781789</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.560103697639512</v>
+        <v>-5.547124555241048</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.991559165472218</v>
+        <v>-6.978516269177852</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.972047710097421</v>
+        <v>-3.958866700802183</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4.033047596279722</v>
+        <v>-4.019848857324959</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.88317278130765</v>
+        <v>-4.869767653654819</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.624971519708375</v>
+        <v>-8.611519230988264</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.854749940177079</v>
+        <v>-7.841193893825476</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-12.36693336980556</v>
+        <v>-12.37736300550371</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>117</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.630190456962112</v>
+        <v>-4.617668167286489</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-3.677661505823806</v>
+        <v>-3.664751696247755</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.781931921822107</v>
+        <v>-5.768924790404505</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.942277079812897</v>
+        <v>-3.929297937414432</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-5.335399149585918</v>
+        <v>-5.322288345210978</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.037957211870257</v>
+        <v>-5.024914315575892</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.267990074441684</v>
+        <v>-4.254923820141208</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4616691997189051</v>
+        <v>-0.4484881904236673</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5226690859012066</v>
+        <v>-0.5094703469464434</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.372794270929134</v>
+        <v>-1.359389143276303</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.107267002003844</v>
+        <v>-4.093814713283734</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.818119903547043</v>
+        <v>-2.80456385719544</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.987201990074176</v>
+        <v>-5.997631625772328</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>157</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.085795008108065</v>
+        <v>-4.073272718432442</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.149597920435376</v>
+        <v>-3.136688110859325</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.544466627031966</v>
+        <v>-3.531459495614364</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.140328144106</v>
+        <v>-2.127349001707536</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.67874935917817</v>
+        <v>-2.66563855480323</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.292135446940215</v>
+        <v>-4.279092550645849</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.739926489053254</v>
+        <v>-3.726860234752778</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.8884315134391301</v>
+        <v>0.9016125227343679</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.083396398220884</v>
+        <v>-1.070197659266121</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.570464258408045</v>
+        <v>-2.557059130755214</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2274468820886781</v>
+        <v>-0.2139895883784604</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.740834425380193</v>
+        <v>-2.727382136660083</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6133183356881489</v>
+        <v>-0.599762289336546</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.637482353730334</v>
+        <v>-1.647911989428486</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>203</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.247132901490758</v>
+        <v>-2.234610611815135</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.380874002139748</v>
+        <v>-2.367964192563697</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.775742708736338</v>
+        <v>-2.762735577318736</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.660267901251991</v>
+        <v>-1.647288758853527</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.706078278885734</v>
+        <v>-1.692967474510795</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.39385801604692</v>
+        <v>-2.380815119752555</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.508148383565505</v>
+        <v>-0.4950821292650289</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.472944079721955</v>
+        <v>2.486125089017193</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4415008437859598</v>
+        <v>0.454699582740723</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.393846016118815</v>
+        <v>-1.380440888465984</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1207668281211269</v>
+        <v>-0.1073095344109092</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.564216183090963</v>
+        <v>-1.550763894370853</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.01402744428217062</v>
+        <v>-0.0004713979305677185</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.734749461759577</v>
+        <v>-1.745179097457729</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>259</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.878053704825362</v>
+        <v>-2.865531415149739</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.412704240866539</v>
+        <v>-6.399794431290488</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.079031218921401</v>
+        <v>-5.256104277583987</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.018276155811975</v>
+        <v>-3.005297013413511</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.556697370884145</v>
+        <v>-3.543586566509205</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.417556591469641</v>
+        <v>-4.404513695175275</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.957888764340375</v>
+        <v>-2.944822510039899</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.880670618720323</v>
+        <v>-1.867489609425085</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.486072049304177</v>
+        <v>-3.472873310349414</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.108398006532873</v>
+        <v>-5.094992878880042</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.768749786448915</v>
+        <v>-3.755292492738697</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.664868559605409</v>
+        <v>-5.651416270885299</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.996320081747221</v>
+        <v>-2.982764035395618</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-5.063201066073255</v>
+        <v>-5.073630701771407</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>310</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.332666616029911</v>
+        <v>-2.320144326354288</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.265783637354296</v>
+        <v>-4.252873827778245</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.145041930093406</v>
+        <v>-5.29073202925354</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.079304926518155</v>
+        <v>-3.066325784119691</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.295145496429043</v>
+        <v>-3.282034692054104</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.642864849035966</v>
+        <v>-3.629821952741601</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.11469534050179</v>
+        <v>-2.101629086201314</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.9689755134768276</v>
+        <v>-0.9557945041815898</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.642878625465592</v>
+        <v>-2.629679886510829</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.815584455654808</v>
+        <v>-3.802179328001976</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.084853909004636</v>
+        <v>-2.071396615294418</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.308535267788244</v>
+        <v>-4.295082979068134</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.470725362604107</v>
+        <v>-2.457169316252504</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.833907256134282</v>
+        <v>-3.844336891832434</v>
       </c>
     </row>
     <row r="12">
@@ -4220,933 +4220,933 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.28700400385609</v>
+        <v>-1.411397313956805</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.434770646310959</v>
+        <v>-3.557342765309407</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.037515048372974</v>
+        <v>-5.28901254578637</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.025541485657946</v>
+        <v>-3.150214048410973</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.295145496429043</v>
+        <v>-3.420407086761358</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.341789580218759</v>
+        <v>-4.463515630852811</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.082437275985662</v>
+        <v>-2.93964690164713</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.667900244659634</v>
+        <v>-1.53003994221671</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.997717335143015</v>
+        <v>-1.859118613484796</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.385476928773087</v>
+        <v>-3.245230439305267</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.977327027284218</v>
+        <v>-1.84135250909361</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.824664300046315</v>
+        <v>-3.683649959955446</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.287929663679385</v>
+        <v>-1.154739151070466</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.651111557209553</v>
+        <v>-2.537582589315782</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.009076</t>
+          <t>X &lt; -0.009072</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>451</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1755575255079904</v>
+        <v>-0.1630352358323677</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.6833783790903496</v>
+        <v>-0.6704685695142985</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.951208073399144</v>
+        <v>-3.051994921156755</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.935999188579252</v>
+        <v>-1.923020046180788</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.0230929700231</v>
+        <v>-4.009982165648161</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.168128908413635</v>
+        <v>-4.15508601211927</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.146667935420432</v>
+        <v>-3.133601681119956</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.9589840775647573</v>
+        <v>-0.9458030682695195</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.019983963747059</v>
+        <v>-1.006785224792296</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.5281944263293</v>
+        <v>-1.635465083069064</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.289488770602524</v>
+        <v>-1.276031476892307</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.585482553390129</v>
+        <v>-2.572030264670019</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3449832840689595</v>
+        <v>-0.3314272377173566</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.647368381947878</v>
+        <v>-1.65779801764603</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.008097</t>
+          <t>X &lt; -0.008094</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2165712892445839</v>
+        <v>-0.1172796668979856</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.463846177254382</v>
+        <v>-1.364829396325462</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.134917136121182</v>
+        <v>-4.123237144716853</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.72977375944852</v>
+        <v>-3.71912559609455</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.547902469950301</v>
+        <v>-5.44238317333501</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-5.98172195819442</v>
+        <v>-5.87493615099919</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.152378893016973</v>
+        <v>-5.047237751141267</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.511701231469409</v>
+        <v>-2.594598365730924</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.389885761161757</v>
+        <v>-2.473098770428884</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.960095858230723</v>
+        <v>-3.140535814933934</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.24909826679739</v>
+        <v>-2.334414837857381</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.313616208353054</v>
+        <v>-3.396928824441723</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.169768255195393</v>
+        <v>-1.2576646868959</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.385248388120573</v>
+        <v>-2.494451888588934</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.007118</t>
+          <t>X &lt; -0.007115</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4068849971806117</v>
+        <v>-0.5548759689010723</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4728635560490417</v>
+        <v>-0.4711468077276137</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.106691785281654</v>
+        <v>-3.023083061511926</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.121565491659453</v>
+        <v>-2.041833549950042</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.210374303630836</v>
+        <v>-4.044860638107849</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.223009885295028</v>
+        <v>-4.056605619291922</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.462782362257222</v>
+        <v>-4.450434989377257</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.22453940444958</v>
+        <v>-3.217349073658589</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.355306732492345</v>
+        <v>-2.350974197723872</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.50222040035527</v>
+        <v>-2.582654972415398</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.157095919740605</v>
+        <v>-2.240177200533616</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.67792271573888</v>
+        <v>-3.672427315152156</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.076404387336972</v>
+        <v>-2.077074292496576</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.070851017735642</v>
+        <v>-3.091648719789418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006139</t>
+          <t>X &lt; -0.006136</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>752</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.170686997458652</v>
+        <v>-1.15816470778303</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.062683890846188</v>
+        <v>-1.049774081270137</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.917099182817182</v>
+        <v>-1.973645995125707</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.9213516450943615</v>
+        <v>-0.9791649210562525</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.714414769980849</v>
+        <v>-3.701303965605909</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.682224821655112</v>
+        <v>-3.669181925360746</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.634332544232429</v>
+        <v>-3.621266289931953</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.907881990759286</v>
+        <v>-2.894700981464048</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.642621929991982</v>
+        <v>-1.629423191037219</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.491975665010933</v>
+        <v>-1.550960024502359</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.8262746365269535</v>
+        <v>-0.8864589466143116</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.387636160032585</v>
+        <v>-2.374183871312475</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.9461886433179174</v>
+        <v>-0.9326325969663145</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.760297098275664</v>
+        <v>-1.770726733973817</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.00516</t>
+          <t>X &lt; -0.005157</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5903241333587701</v>
+        <v>-0.5223906849122315</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7024744475917615</v>
+        <v>-0.6358809254414979</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.728518053165736</v>
+        <v>-1.721896549827875</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.03436739155639401</v>
+        <v>-0.03138884919392382</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.422499589287519</v>
+        <v>-2.354522213472563</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.893843778739488</v>
+        <v>-1.82620130162038</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.631756686763204</v>
+        <v>-1.564491337560924</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.17408459421523</v>
+        <v>-1.107772452479296</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.03659182018049734</v>
+        <v>0.1014532431919264</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.06061028747541286</v>
+        <v>0.059848534621878</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3844018753933653</v>
+        <v>0.3824538415394372</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.7399635188255189</v>
+        <v>-0.6750112944803206</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1144052769503219</v>
+        <v>0.1779860003544229</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7946219423376917</v>
+        <v>-0.7536857568264637</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004181</t>
+          <t>X &lt; -0.004178</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1363671065690468</v>
+        <v>-0.1763068120974793</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1577764319210502</v>
+        <v>0.216515110870759</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.8854228084455187</v>
+        <v>-0.8796590794955037</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3037393270075341</v>
+        <v>0.3073436111629277</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.340209526255585</v>
+        <v>-1.280480086535249</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7412600508514871</v>
+        <v>-0.6819012376230518</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.9264962806865853</v>
+        <v>-0.8670132033149258</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3148630340997585</v>
+        <v>0.272343855709579</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.158385760982782</v>
+        <v>1.114976157018127</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8680009276125347</v>
+        <v>0.7670653928167752</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.224115327262126</v>
+        <v>1.222492183538442</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5535639428150105</v>
+        <v>0.6104794276301178</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.140358677288035</v>
+        <v>1.095761169890153</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1816207950628055</v>
+        <v>0.114253359352098</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003202</t>
+          <t>X &lt; -0.0032</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1149</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.802198077365226</v>
+        <v>-0.7896757876896032</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.07205443100597364</v>
+        <v>-0.05914462142992249</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.548491750881936</v>
+        <v>-1.581409501414804</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.242781286485652</v>
+        <v>-0.2767872536537439</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.910655151427498</v>
+        <v>-1.897544347052559</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.265689321444242</v>
+        <v>-1.252646425149877</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.176661092582727</v>
+        <v>-1.163594838282251</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6012728145614474</v>
+        <v>-0.5880918052662096</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.075346760594222</v>
+        <v>1.088545499548985</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.9698292890857232</v>
+        <v>0.9336744877543097</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.510979775264985</v>
+        <v>1.474185432391401</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.110201923036875</v>
+        <v>1.123654211756985</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.212140523580231</v>
+        <v>1.225696569931834</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6785720386241394</v>
+        <v>0.6681424029259873</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.002223</t>
+          <t>X &lt; -0.002221</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1315</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.242490632567822</v>
+        <v>-1.229968342892199</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2005388475032674</v>
+        <v>-0.1876290379272163</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.9338715350667286</v>
+        <v>-0.9614754795435161</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4592250773987061</v>
+        <v>-0.4871491234902052</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.908808023678162</v>
+        <v>-1.895697219303223</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.383575653160683</v>
+        <v>-1.370532756866318</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9367983605620367</v>
+        <v>-0.9237321062615607</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.03723916253260739</v>
+        <v>-0.02405815323736959</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9647829710269207</v>
+        <v>0.9779817099816839</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.7652568032921465</v>
+        <v>0.7355040677900249</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8318638635943998</v>
+        <v>0.8019242985206461</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6381101388105535</v>
+        <v>0.6515624275306635</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.130403056382754</v>
+        <v>1.143959102734357</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.5436224875183697</v>
+        <v>0.5331928518202176</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.001244</t>
+          <t>X &lt; -0.001242</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1521</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5590120907017706</v>
+        <v>-0.5464898010261479</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.05892249305527741</v>
+        <v>0.07183230263132856</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3660223720542817</v>
+        <v>-0.3885128526155128</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6598441847733056</v>
+        <v>-0.6821076823501642</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.132605518033259</v>
+        <v>-1.11949471365832</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.9008234621298143</v>
+        <v>-0.887780565835449</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3289583612799589</v>
+        <v>-0.3158921069794829</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.320076230746146</v>
+        <v>0.3332572400413838</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.243974571747039</v>
+        <v>1.257173310701802</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.350792552526279</v>
+        <v>1.32649285974292</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.381032286410083</v>
+        <v>1.356605588935999</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.152430565386027</v>
+        <v>1.165882854106137</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.5211305895496</v>
+        <v>1.534686635901203</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.113389725902159</v>
+        <v>1.102960090204007</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.000265</t>
+          <t>X &lt; -0.0002631</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.007562613995283129</v>
+        <v>0.004959675680339615</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2452705527014771</v>
+        <v>0.2581803622775283</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.401519984033115</v>
+        <v>-0.4190768981837252</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.5409332714918307</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8922116181630955</v>
+        <v>-0.8791008137881562</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.9906972822573863</v>
+        <v>-0.9776543859630209</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2270147099369098</v>
+        <v>-0.2139484556364337</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6632679546300082</v>
+        <v>0.676448963925246</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.9981956702576653</v>
+        <v>1.011394409212429</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6326328618324624</v>
+        <v>0.6139643006653728</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4599895498782018</v>
+        <v>0.4413368312251009</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5509978487864799</v>
+        <v>0.56445013750659</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.753619795032975</v>
+        <v>0.767175841384578</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4693002737935288</v>
+        <v>0.4832852175454221</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0007139</t>
+          <t>X &lt; 0.0007157</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1640419947506473</v>
+        <v>0.17656428442627</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.09221035759570384</v>
+        <v>-0.1058816511572331</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.4604717727757475</v>
+        <v>-0.4740719327746916</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.8457241064733267</v>
+        <v>-0.8591114189520539</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.357752864247331</v>
+        <v>-1.371034517170557</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.454788244085904</v>
+        <v>-1.441745347791539</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.069292154480813</v>
+        <v>-1.082668724809189</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4511277486249199</v>
+        <v>-0.4379467393296821</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.326550214230771</v>
+        <v>0.3397489531855342</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.002572959937836572</v>
+        <v>-0.01682993194551585</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1302541479532735</v>
+        <v>-0.1445106489854737</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.002894441490930433</v>
+        <v>0.01634673021104049</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1258497070892304</v>
+        <v>0.1394057534408333</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2060009422591875</v>
+        <v>0.2169932555192275</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.001693</t>
+          <t>X &lt; 0.001695</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5721920770266422</v>
+        <v>0.584714366702265</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8004762960252023</v>
+        <v>-0.8105822617674434</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.042663699407818</v>
+        <v>-1.052748238374818</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.9757667203064244</v>
+        <v>-0.9858618479109253</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.361335919467322</v>
+        <v>-1.371375444881735</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.453167338153051</v>
+        <v>-1.440124441858686</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.082186023211406</v>
+        <v>-1.092308849567758</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5541292662161936</v>
+        <v>-0.5409482569209558</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1391447300704911</v>
+        <v>-0.1259459911157279</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.4892333873682588</v>
+        <v>-0.4998803651175905</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3667522311382285</v>
+        <v>-0.3774991149453157</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.07251632368452476</v>
+        <v>-0.0590640349644147</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.3734048990648091</v>
+        <v>0.386960945416412</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.2578912567521741</v>
+        <v>0.2662262621652474</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.002672</t>
+          <t>X &lt; 0.002673</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1345829451133085</v>
+        <v>-0.1220606554376857</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3719364979711415</v>
+        <v>-0.3798051398394833</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.055608193950391</v>
+        <v>-1.0632758294364</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.214381668990654</v>
+        <v>-1.221973442164234</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.577297366697152</v>
+        <v>-1.58483338824383</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.20239609513176</v>
+        <v>-1.189353198837395</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.8402455773442199</v>
+        <v>-0.8480372219300492</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6100248691904255</v>
+        <v>-0.5968438598951877</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2835780292975585</v>
+        <v>-0.2703792903427953</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4147342431016625</v>
+        <v>-0.4228939797373599</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.210158790866835</v>
+        <v>-0.2184333744842206</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.253325071287982</v>
+        <v>-0.2398727825678719</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1475941531143832</v>
+        <v>-0.1559522903985311</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1475753122635624</v>
+        <v>-0.1410410135571993</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.003651</t>
+          <t>X &lt; 0.003652</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.292398458858159</v>
+        <v>-0.2979638475821744</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.429561170344833</v>
+        <v>-0.4352563696986991</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8751841430659937</v>
+        <v>-0.8807708731243693</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.628475529370121</v>
+        <v>-1.633790230876549</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.662647819771067</v>
+        <v>-1.66801217185084</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.191655031656246</v>
+        <v>-1.178612135361881</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.014784946236553</v>
+        <v>-1.020351304069209</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.8033714170723911</v>
+        <v>-0.8090651135005942</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4822941931470268</v>
+        <v>-0.4690954541922636</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7227108202897483</v>
+        <v>-0.7285314439920754</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2478148786526901</v>
+        <v>-0.25382616986861</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.4914991526593582</v>
+        <v>-0.4780468639392481</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.3012695772391396</v>
+        <v>-0.3073044256294395</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.3449872000333016</v>
+        <v>-0.3401419974899298</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.00463</t>
+          <t>X &lt; 0.004631</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.05945804658605169</v>
+        <v>-0.0636132315521607</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3494422323467319</v>
+        <v>-0.3536356902542437</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9818927378287654</v>
+        <v>-0.9859187024970808</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.790009672768413</v>
+        <v>-1.793770300454135</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.610820305542283</v>
+        <v>-1.614683140790483</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.168924184137417</v>
+        <v>-1.172906353978888</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.204744390858089</v>
+        <v>-1.208724215624201</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9852279822062613</v>
+        <v>-0.9893173892063345</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5360237867559121</v>
+        <v>-0.5228250478011489</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.7626441870948426</v>
+        <v>-0.7668764971922357</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3434948296049356</v>
+        <v>-0.3478796116416021</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3091116722595046</v>
+        <v>-0.2956593835393946</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.105065323272548</v>
+        <v>-0.1095562483397146</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.06078485676048473</v>
+        <v>-0.05728336177261184</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.005609</t>
+          <t>X &lt; 0.00561</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3366</v>
+        <v>3368</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1392778227270028</v>
+        <v>-0.1281489396790718</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4024052981031403</v>
+        <v>-0.3916876771801796</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.8998806397708208</v>
+        <v>-0.918617659967083</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.257594312142572</v>
+        <v>-1.27607964438571</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.157678132256244</v>
+        <v>-1.176419399342031</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.8146399992292004</v>
+        <v>-0.8038472314382688</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.9427448328511403</v>
+        <v>-0.9615508558521455</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7708325059148535</v>
+        <v>-0.7899122862961647</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.446075715539294</v>
+        <v>-0.4491265903701205</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.330104893422309</v>
+        <v>-0.3497721740034478</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.221395170210684</v>
+        <v>-0.2412061299876385</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.187012012865253</v>
+        <v>-0.1605163899587083</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.0857171711443101</v>
+        <v>-0.07606647152975654</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.0568578244358946</v>
+        <v>-0.04137160181634414</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.006588</t>
+          <t>X &lt; 0.006589</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3557</v>
+        <v>3559</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2104002900449942</v>
+        <v>0.2214082483791202</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.06913749371234701</v>
+        <v>-0.05848867822003001</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6731354757674595</v>
+        <v>-0.6622727798578438</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.032555157191361</v>
+        <v>-1.02144657104288</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.8547527895566702</v>
+        <v>-0.8439146490071678</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6263194668991829</v>
+        <v>-0.6155111680908547</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.6397693538830467</v>
+        <v>-0.6289783148128123</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5022207001244183</v>
+        <v>-0.4916549002570534</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1828048875702848</v>
+        <v>-0.1724356287722415</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.0218566461936831</v>
+        <v>0.03183925525136289</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.00145159544114648</v>
+        <v>0.01138187208226071</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.09203031333729683</v>
+        <v>0.1177477567057039</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.03133389585041613</v>
+        <v>-0.0215042202032194</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.07494038481284804</v>
+        <v>-0.06083482075410984</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3712</v>
+        <v>3713</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.3529633983721965</v>
+        <v>0.3512987345663205</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1431532170850573</v>
+        <v>-0.1447337025455511</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3891874640588355</v>
+        <v>-0.3907144968033904</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6206353007671908</v>
+        <v>-0.6220970482683512</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5263282921279639</v>
+        <v>-0.5278323010908679</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2411526301772611</v>
+        <v>-0.2427251785480422</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3650554022762336</v>
+        <v>-0.3665979904332772</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1719400964304896</v>
+        <v>-0.173549453946471</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.00285640247174257</v>
+        <v>-0.004513909786624026</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1309270712848019</v>
+        <v>0.1292071784739477</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.05869308770077453</v>
+        <v>-0.06036895932255959</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1910912543511714</v>
+        <v>0.2045435430712814</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.1331668280741738</v>
+        <v>-0.1348318659771834</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1106731070797764</v>
+        <v>-0.1093343289105277</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3825</v>
+        <v>3826</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1518574838035747</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1946886797852869</v>
+        <v>-0.195828993548659</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3408193620654743</v>
+        <v>-0.3419308597609358</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.535511701216528</v>
+        <v>-0.5365701379069634</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.5902819599083315</v>
+        <v>-0.5913385438386456</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2264731728288112</v>
+        <v>-0.2276186755982863</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3231139290956833</v>
+        <v>-0.3242366692035361</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1233594097119948</v>
+        <v>-0.1245451883287458</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.03940260629104131</v>
+        <v>-0.04061225406746871</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.09145029676371053</v>
+        <v>0.0901870777807261</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.04636675912728094</v>
+        <v>-0.04759912987291415</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2231875505567871</v>
+        <v>0.2366398392768971</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.02678741078002389</v>
+        <v>0.02553001026450374</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.08217960871918706</v>
+        <v>0.08312040375126628</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3931</v>
+        <v>3932</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2195434242119276</v>
+        <v>0.2187037413287598</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.009145841365970853</v>
+        <v>-0.009952022178303821</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3141880979138989</v>
+        <v>-0.3149232166971174</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3731799050318827</v>
+        <v>-0.3738984916040309</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5679471993928473</v>
+        <v>-0.568624799362702</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1551612399653735</v>
+        <v>-0.1559395227432319</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.302247561213143</v>
+        <v>-0.3029901652372615</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1968139691537516</v>
+        <v>-0.1975907328223059</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.0914099656177072</v>
+        <v>-0.0922148115806749</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.06358101550968343</v>
+        <v>0.06272363554379012</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1014831298584085</v>
+        <v>-0.1023020544877724</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.09973880683262593</v>
+        <v>0.09886883883041264</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.0009980630274384339</v>
+        <v>-0.001849155167235494</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.008749541364508673</v>
+        <v>0.009402484008475653</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2220574446131423</v>
+        <v>0.2214500964893062</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01908475259700992</v>
+        <v>0.01851073140930026</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2625925041776043</v>
+        <v>-0.2631007697536702</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1936115510426504</v>
+        <v>-0.1941359021526878</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3444576997915973</v>
+        <v>-0.3449503835798211</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1082371162733864</v>
+        <v>-0.1087858333626244</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1793724379198522</v>
+        <v>-0.1799045792451892</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.009042493036801602</v>
+        <v>-0.009622332396141076</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.006349548113867343</v>
+        <v>-0.006930987406839506</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1061263091150408</v>
+        <v>0.105507528809575</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.04027902257990235</v>
+        <v>0.03967422357634121</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1386938265200541</v>
+        <v>0.1380645185954918</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.08235293695578605</v>
+        <v>0.08173295865421437</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.02133860981858504</v>
+        <v>0.02179455857139345</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.02596962391731239</v>
+        <v>-0.02632594707828417</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1266229351388688</v>
+        <v>-0.1269658604015262</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2871564933694444</v>
+        <v>-0.2874628993158979</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2418633793991916</v>
+        <v>-0.242180175130855</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3000369257252871</v>
+        <v>-0.3003433232659631</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.136663815001647</v>
+        <v>-0.1370084692035931</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1834152497635841</v>
+        <v>-0.1837491737453192</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.09611957199515331</v>
+        <v>-0.09647837197667997</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.04517200323807913</v>
+        <v>-0.04554393614350261</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.004106933727967998</v>
+        <v>0.00371679547538406</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.01455784618755729</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.08291340678807302</v>
+        <v>0.08250231068279845</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.02127168245867495</v>
+        <v>0.02087264623220619</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.01061153072509313</v>
+        <v>-0.01030586499174291</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.0672008171619396</v>
+        <v>-0.06745918021743336</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1050119331742323</v>
+        <v>-0.1052696437152321</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1451599761943356</v>
+        <v>-0.1454100937190717</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1236538614825022</v>
+        <v>-0.1239086721569009</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1850806968510597</v>
+        <v>-0.185323471789296</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1184192845198311</v>
+        <v>-0.1186768977446278</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1898459962976062</v>
+        <v>-0.1900867474916339</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1551961037978344</v>
+        <v>-0.1554478973833753</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.08059683830734343</v>
+        <v>-0.0808673047625561</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.01304291117778433</v>
+        <v>-0.01333448669147685</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.008541626338526953</v>
+        <v>-0.008835520475258818</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.08849919865232181</v>
+        <v>0.08818162222029713</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.07331490278138375</v>
+        <v>0.07299867806879945</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.04337321858323406</v>
+        <v>0.04359217040378383</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_7.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_7.xlsx
@@ -568,1353 +568,1353 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01544</t>
+          <t>X ≈ -0.01552</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.983048764606934</v>
+        <v>-2.501828783293568</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.611884170228578</v>
+        <v>-4.081028074528682</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.05882092147720641</v>
+        <v>4.87522049330353</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.188637088435172</v>
+        <v>5.005876165004651</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.395659340619275</v>
+        <v>-1.717334486362311</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.05166381189070535</v>
+        <v>4.792333621042118</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.161404831769708</v>
+        <v>1.613239552828915</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.474687763771982</v>
+        <v>13.63002315803238</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.415865421854839</v>
+        <v>13.59643636175588</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.568835064525025</v>
+        <v>9.654775393547808</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.42225313592124</v>
+        <v>15.69855022586339</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.402274604042972</v>
+        <v>9.513584639737893</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.01354033597107</v>
+        <v>12.24502413030455</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.24168461354116</v>
+        <v>12.49701670644391</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01446</t>
+          <t>X ≈ -0.01453</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.472550165484463</v>
+        <v>-3.717268144813453</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.586953796110556</v>
+        <v>-2.864916648058738</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.005300200597311</v>
+        <v>1.606476910571324</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.135840814644318</v>
+        <v>1.736337036321132</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.094005723128184</v>
+        <v>3.682259779681139</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.093043764869606</v>
+        <v>-3.347152565954637</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.178166223295115</v>
+        <v>-3.40856645044024</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.843524991202912</v>
+        <v>3.431439742862395</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.706835151338872</v>
+        <v>-3.912616220482711</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.054092335663178</v>
+        <v>-7.173194862488714</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.23421043205893</v>
+        <v>2.369855787434275</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.268901412669145</v>
+        <v>2.428605498068038</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.847867156203868</v>
+        <v>6.910929108792274</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.07501794687725</v>
+        <v>9.600675243029279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01348</t>
+          <t>X ≈ -0.01355</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.028083480567304</v>
+        <v>6.559881880938477</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2554149435664925</v>
+        <v>0.4512263522955848</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1383329307312806</v>
+        <v>0.05855779244850368</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.008575357555493213</v>
+        <v>0.1880298481073694</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.623373278029398</v>
+        <v>1.967560533772939</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.09024629572189</v>
+        <v>4.508617794481736</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.51692977075724</v>
+        <v>6.717897172915123</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.882256211912733</v>
+        <v>3.984822310686212</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.652277815740732</v>
+        <v>3.949019550945401</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.632940417271037</v>
+        <v>-1.413856679984505</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2566699626880435</v>
+        <v>-3.889325179468223</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.463940033269587</v>
+        <v>-1.560546410554807</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.04444671509367</v>
+        <v>0.3160963332949933</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.07715596616525</v>
+        <v>-3.980256020829856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.0125</t>
+          <t>X ≈ -0.01257</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.189248225713399</v>
+        <v>-3.473143134956082</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-21.07252540232937</v>
+        <v>-18.85013098804169</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-14.35362713789735</v>
+        <v>-11.86093845736315</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.907642010728338</v>
+        <v>-9.887350181665823</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.22834575044421</v>
+        <v>-14.073251323146</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-11.7161599635361</v>
+        <v>-11.95639869878092</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-11.8038729646543</v>
+        <v>-8.322938786856568</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-17.62243398888489</v>
+        <v>-12.48849349231504</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-17.68765288621393</v>
+        <v>-16.22745107445036</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-18.54113674857117</v>
+        <v>-13.35452574861372</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-16.96615717724026</v>
+        <v>-13.56200171405826</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-20.50571909406045</v>
+        <v>-17.20912673648165</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-13.79002971323093</v>
+        <v>-12.05449473693195</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-17.13926776740847</v>
+        <v>-13.6603907009635</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01152</t>
+          <t>X ≈ -0.01159</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4593556560076948</v>
+        <v>-0.6558328037720713</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.674503296968538</v>
+        <v>1.458978222640368</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.452298182854378</v>
+        <v>-8.166785355437668</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.36700942348044</v>
+        <v>-2.498300073570448</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.948658970832994</v>
+        <v>0.7081441505011412</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3044361581087358</v>
+        <v>-0.8674890419934655</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.176983910832789</v>
+        <v>0.9200464970229305</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.668771327788214</v>
+        <v>-1.394026808900286</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.650689987367343</v>
+        <v>0.4183202786186371</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.760864435000713</v>
+        <v>-0.4045431487110918</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.475384030335789</v>
+        <v>3.09206577943322</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.59185879515671</v>
+        <v>-0.55080897031565</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2120460594935594</v>
+        <v>-2.797537682997429</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.398547358641956</v>
+        <v>1.154424113852158</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01054</t>
+          <t>X ≈ -0.01061</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.065477738247871</v>
+        <v>1.749916530783423</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1224124270563607</v>
+        <v>0.1405910015146361</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.26559910852572</v>
+        <v>-5.417944181642838</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.552983976441269</v>
+        <v>-3.565500422803147</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.090957708047469</v>
+        <v>-4.06335087833817</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-8.547142514130748</v>
+        <v>-8.951298794645894</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.04982142966935</v>
+        <v>-7.292361571168236</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.348610721818389</v>
+        <v>-3.370417305925933</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.930382114342798</v>
+        <v>0.03567471466571703</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.5037456235480491</v>
+        <v>-0.7872605463583682</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.7086299335457795</v>
+        <v>0.7311500771032655</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.6744290751707425</v>
+        <v>0.7894999329295729</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.25273692856338</v>
+        <v>7.289243239466359</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.89247826433828</v>
+        <v>4.091844292650805</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.009561</t>
+          <t>X ≈ -0.009627</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.802316726135004</v>
+        <v>6.993433309956785</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>13.1239977595948</v>
+        <v>11.35060000228538</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.611483406153191</v>
+        <v>6.211898617378139</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.908100941630146</v>
+        <v>2.779754450397029</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.869661468539626</v>
+        <v>-7.211190301019528</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.733438800519032</v>
+        <v>-3.37594092102691</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.098570519795985</v>
+        <v>-4.626291521581031</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.831044923467253</v>
+        <v>0.8512527835821473</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.04976845545702</v>
+        <v>3.192379785880689</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.03180066842507</v>
+        <v>4.748727496222216</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.426430078364014</v>
+        <v>-0.2122765877063344</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.742560295857679</v>
+        <v>1.035666595581098</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.604778518507956</v>
+        <v>4.211180168441864</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.549376921235634</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.008583</t>
+          <t>X ≈ -0.008644</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.09716289978000248</v>
+        <v>-1.966657158640139</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.644942982707875</v>
+        <v>-5.68858607268055</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-9.203687399278415</v>
+        <v>-8.226918477363114</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-12.1896066184622</v>
+        <v>-10.24517526108787</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-12.15868954520274</v>
+        <v>-9.662775679103319</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-13.94460545846225</v>
+        <v>-12.61282538298887</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-14.03332316176795</v>
+        <v>-11.60365334967573</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-10.3431701205128</v>
+        <v>-6.701635208039711</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-9.366426392088712</v>
+        <v>-7.814199706202174</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-10.21821748796371</v>
+        <v>-8.639248859080645</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.300368846973996</v>
+        <v>-4.548163317674913</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-7.268002910458073</v>
+        <v>-4.491266950483094</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.607468324177681</v>
+        <v>-4.887755674126225</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.424982053123223</v>
+        <v>-4.640080067749643</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.007605</t>
+          <t>X ≈ -0.007662</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.008716902224357</v>
+        <v>0.4883991107474088</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.527433935455718</v>
+        <v>6.886213559294085</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.109269783938394</v>
+        <v>2.507491293770912</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7.314399626896837</v>
+        <v>4.632403737493661</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.714400726515336</v>
+        <v>1.15271597630678</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6.051681825349952</v>
+        <v>4.419399526084405</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.164217311690528</v>
+        <v>-2.628531544883586</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.728998761376168</v>
+        <v>-9.084075735673416</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.694967564729616</v>
+        <v>-2.133447315525345</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5048202406694031</v>
+        <v>0.03965449971552459</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.740337204178132</v>
+        <v>-4.161177999097816</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.206863891304337</v>
+        <v>-7.102548128131936</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.648752810937509</v>
+        <v>-8.499564272726509</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.424982053122285</v>
+        <v>-8.252983293556319</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.006625</t>
+          <t>X ≈ -0.006681</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.804520305864877</v>
+        <v>-5.271014604844787</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.54847066358132</v>
+        <v>-4.079890821187782</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.383754554900108</v>
+        <v>3.836620866032092</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.446073065951389</v>
+        <v>4.890353397203427</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.619065144703121</v>
+        <v>-2.062068804341997</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.322849858343858</v>
+        <v>-0.8665423157963659</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.391743536576961</v>
+        <v>0.921167284757594</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.941868588910495</v>
+        <v>-1.392843723401349</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.731664725025681</v>
+        <v>1.343189978077433</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.685013181785877</v>
+        <v>4.220002289241783</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.282494924830701</v>
+        <v>6.792446714826895</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.448938731414763</v>
+        <v>5.001773106635945</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.96450035553103</v>
+        <v>5.533534339905898</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>6.191840376784008</v>
+        <v>5.784053743481365</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.005647</t>
+          <t>X ≈ -0.005699</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.759485516289452</v>
+        <v>1.613522422944456</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.153339231078249</v>
+        <v>0.9502094635209701</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.021666286944658</v>
+        <v>-0.3562903483191278</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.344687865177768</v>
+        <v>7.092254298854016</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.6997722906764</v>
+        <v>6.607604988268477</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>10.56338492711569</v>
+        <v>9.628056308314996</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>12.26478385714118</v>
+        <v>11.40173140878127</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.90974953288438</v>
+        <v>10.0206968100023</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>11.74372661044873</v>
+        <v>11.81834882558018</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>10.89772103678474</v>
+        <v>10.08252836426439</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>8.908419541807717</v>
+        <v>8.964780138220149</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>10.72760979148146</v>
+        <v>9.942573959448559</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.632781864175328</v>
+        <v>6.798772696965642</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.075017946877047</v>
+        <v>5.214906614700375</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.004667</t>
+          <t>X ≈ -0.004717</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.128756177092285</v>
+        <v>2.783716866024143</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.893579835982955</v>
+        <v>4.981176638666227</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.734414724864877</v>
+        <v>4.590853170396223</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.560825177649917</v>
+        <v>2.454227127090711</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.862756839190112</v>
+        <v>4.991202130465553</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>6.928793400252097</v>
+        <v>6.020446517161247</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.77407952359215</v>
+        <v>2.936915978287324</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>9.454597448718069</v>
+        <v>8.520994633668913</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>7.859250662699488</v>
+        <v>6.973385037487226</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.47482738805197</v>
+        <v>4.639486553973214</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.807696443440186</v>
+        <v>5.193757290731341</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>9.148467894709505</v>
+        <v>9.039186337654364</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.19319110972075</v>
+        <v>7.889470763693858</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.882710254569552</v>
+        <v>7.383380342807541</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.003689</t>
+          <t>X ≈ -0.003736</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.724833737153901</v>
+        <v>-5.736084408265597</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.829274235502716</v>
+        <v>-1.490445394899609</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-6.08510609103319</v>
+        <v>-4.471452642765676</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.024954336670703</v>
+        <v>-2.402157096724004</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.848194405457988</v>
+        <v>-3.537148877459529</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.909900089688833</v>
+        <v>-3.26664437023129</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.063738432708192</v>
+        <v>-2.032056435158438</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.109020882957218</v>
+        <v>-5.089925536496395</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.9175539875566159</v>
+        <v>1.353915168068966</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.002858731275737</v>
+        <v>2.477296760985681</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.087668885140864</v>
+        <v>4.220236819978467</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4.411620682712119</v>
+        <v>4.279900869912943</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.058201176144443</v>
+        <v>1.289681825945188</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.220179237199972</v>
+        <v>2.188575148002649</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002711</t>
+          <t>X ≈ -0.002754</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>166</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.273829456726638</v>
+        <v>-4.018014402778959</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.076861677846118</v>
+        <v>-0.2018067128745002</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.337691258580165</v>
+        <v>1.20361784093852</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.941974615902076</v>
+        <v>-2.869558123722783</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.876505045833163</v>
+        <v>-3.363764130787182</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.182256605663106</v>
+        <v>-2.489492303370589</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.739024880110108</v>
+        <v>0.4552676119244694</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.881788405090816</v>
+        <v>4.197850029905361</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2108207980611709</v>
+        <v>0.2836774913315168</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6382811724291599</v>
+        <v>-0.5387492607670907</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.852924196052747</v>
+        <v>-4.353671808272296</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.614499968335302</v>
+        <v>-3.092843459364502</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5778721828056561</v>
+        <v>0.12433035450902</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.4008856675807237</v>
+        <v>-0.2288869080140614</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001731</t>
+          <t>X ≈ -0.001772</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.818624048165773</v>
+        <v>2.873311946938649</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.728318547793286</v>
+        <v>-0.1706862846268109</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.272579801221177</v>
+        <v>3.346370931005801</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.923770460012882</v>
+        <v>-2.877248956383738</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.835130466552684</v>
+        <v>3.480177347656308</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.195112954922116</v>
+        <v>0.8182240010469854</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.564384099447715</v>
+        <v>2.714579628391888</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.613843333501158</v>
+        <v>1.270253608612741</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.038286871497505</v>
+        <v>2.700468238652348</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.100791219750853</v>
+        <v>4.326451349445556</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.896221806158934</v>
+        <v>4.613903138310349</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.44555522953646</v>
+        <v>4.184045446059756</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.027221813744532</v>
+        <v>3.7905473758196</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.740066490566562</v>
+        <v>4.531330431934101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.0007526</t>
+          <t>X ≈ -0.000791</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.425693770631689</v>
+        <v>4.673766848683748</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.41342300243771</v>
+        <v>2.686277846066019</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6069891729654699</v>
+        <v>-0.9845456993503703</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.337413465614901</v>
+        <v>0.3756571720313531</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6153734375054185</v>
+        <v>1.119489754428876</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.531135021735899</v>
+        <v>-0.2503614466579904</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.4194497156018073</v>
+        <v>1.330814201330973</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.805006268793136</v>
+        <v>3.739943529444226</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5165470091224762</v>
+        <v>0.82723905509215</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.812705059326959</v>
+        <v>-1.638088100328993</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.240723008381622</v>
+        <v>-3.075468728073517</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.167160292365089</v>
+        <v>-1.784752046264124</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.996308504997494</v>
+        <v>-2.180404626692244</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.363757563326836</v>
+        <v>-1.931995639235197</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002263</t>
+          <t>X ≈ 0.0001907</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.347927785096736</v>
+        <v>1.193018468534639</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.587801704105004</v>
+        <v>-2.610678256714252</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8530759985899081</v>
+        <v>0.3277876885161888</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.034073231249501</v>
+        <v>-1.765599778003548</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.732209802613582</v>
+        <v>-3.739380296627637</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.605773406685643</v>
+        <v>-4.581038358048268</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-7.004413723545504</v>
+        <v>-6.127600185341642</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-8.030886085036869</v>
+        <v>-7.335244563207766</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.239996595571995</v>
+        <v>-4.403287896104246</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.31906017940468</v>
+        <v>-4.860066348629246</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.137711195641685</v>
+        <v>-4.695842040117753</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.717707664988112</v>
+        <v>-3.524806934997919</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.139334349876044</v>
+        <v>-4.293917140146753</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.598727226867837</v>
+        <v>-1.606143144857121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.001205</t>
+          <t>X ≈ 0.001172</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.493092260344113</v>
+        <v>3.944731628966416</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-5.836586190709042</v>
+        <v>-5.504897610356679</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.176105910512554</v>
+        <v>-5.541004469667506</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.884598980903327</v>
+        <v>-2.187913187184613</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.366642822639882</v>
+        <v>-1.958561969748473</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.420936510788096</v>
+        <v>-1.687637532454623</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.156249363961876</v>
+        <v>-1.39163031935913</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.27225783250703</v>
+        <v>-1.498712177524119</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.44448539201197</v>
+        <v>-4.049696248408907</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.943152051369445</v>
+        <v>-4.514628245741946</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.037092581652701</v>
+        <v>-2.564889103671575</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.5959727253035254</v>
+        <v>-1.429781404752731</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.150959631050327</v>
+        <v>1.411640909176739</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.6172714680040059</v>
+        <v>-0.1378753798869425</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.002184</t>
+          <t>X ≈ 0.002154</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.18776502562411</v>
+        <v>-6.52238990154315</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.318013178428174</v>
+        <v>3.247174846374342</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.156458245300719</v>
+        <v>-1.166220312882722</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.250943000368707</v>
+        <v>-3.234929654750054</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.419641913279683</v>
+        <v>-2.990698538494712</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.9569156827132872</v>
+        <v>0.9440099045708621</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.243229338007446</v>
+        <v>1.248525236820896</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.07869333656889</v>
+        <v>-1.051371810460942</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.51114848099369</v>
+        <v>-1.45600215588928</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2343126681168997</v>
+        <v>0.657050096887744</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.143988854022624</v>
+        <v>1.187293216256272</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.792423145707573</v>
+        <v>-1.326408810497334</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.815602043124144</v>
+        <v>-4.296145802630242</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.636877963903508</v>
+        <v>-3.311806822967945</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.003162</t>
+          <t>X ≈ 0.003136</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.822842979424387</v>
+        <v>-2.338172932266993</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9165162918492769</v>
+        <v>-1.940801003149119</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6960575181692334</v>
+        <v>-0.357505423200827</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.20024188588328</v>
+        <v>-6.161913464794537</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.391741708820504</v>
+        <v>-3.358202893509009</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.089068645813043</v>
+        <v>-1.769250799687001</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.515643401054767</v>
+        <v>-3.484119955611057</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.647771557151401</v>
+        <v>-3.619712189926922</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.185826549580774</v>
+        <v>-2.995577458099405</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.37239016011798</v>
+        <v>-4.485190476588407</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5593803933577348</v>
+        <v>-1.053753731182113</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.536873886590314</v>
+        <v>-2.983531524581217</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.617160656369457</v>
+        <v>-2.197392393982057</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.062565945740204</v>
+        <v>-2.610599187595831</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.004141</t>
+          <t>X ≈ 0.004117</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.561697091722039</v>
+        <v>1.794505859719642</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5580732982673737</v>
+        <v>0.9830182422669438</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.169264852790789</v>
+        <v>-1.557306797319143</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.595645504357293</v>
+        <v>-3.012344151319283</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.028278068527484</v>
+        <v>-1.145807757351051</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.116693690065098</v>
+        <v>-0.8706827723632742</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.309352810970765</v>
+        <v>-3.071029016422919</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.999705023470732</v>
+        <v>-2.353499722770081</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.120078171551334</v>
+        <v>-0.4166892075743434</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.19348011328686</v>
+        <v>-0.8515462631733683</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.398995351880444</v>
+        <v>-1.05501621917044</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.745677070616949</v>
+        <v>1.995896569411293</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.10414610988029</v>
+        <v>2.391252476839526</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.108091876838337</v>
+        <v>3.826068089843112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.005121</t>
+          <t>X ≈ 0.005099</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9888236986093517</v>
+        <v>0.6278187534865509</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.8954409612050682</v>
+        <v>-0.1173763991611096</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.01154788100286197</v>
+        <v>1.162818649631355</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.642828382601628</v>
+        <v>6.561773068442356</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.680061516631888</v>
+        <v>5.655467664176179</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.124675446820603</v>
+        <v>4.248894782777896</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.342769362376671</v>
+        <v>2.512156868306668</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.875225034377635</v>
+        <v>2.045858013387672</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.5377189918528842</v>
+        <v>0.7484448499333212</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.213147146376443</v>
+        <v>5.800099954752255</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.182099338392817</v>
+        <v>2.238324378165338</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.641243084458623</v>
+        <v>2.296491115530188</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3705588923954011</v>
+        <v>0.6408289872857367</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1707626277282799</v>
+        <v>0.4697057820741577</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.0061</t>
+          <t>X ≈ 0.00608</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>191</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.394648738659711</v>
+        <v>6.091811397597525</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.818170919847283</v>
+        <v>5.047619546082807</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.846794497160367</v>
+        <v>3.627529846864846</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.448955993853751</v>
+        <v>2.206154786184122</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.001055779225872</v>
+        <v>4.839450317889217</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.691132562841155</v>
+        <v>3.020229972605136</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.216843056610841</v>
+        <v>5.049462014285368</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.750666871971532</v>
+        <v>5.104724851202924</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.69414701118594</v>
+        <v>4.020055305762249</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.759035305489512</v>
+        <v>5.812919755244593</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.463095101207536</v>
+        <v>2.997266698548941</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.019576928602945</v>
+        <v>4.626114064186083</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.9409053332999306</v>
+        <v>0.5660346716536679</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.4040396447457582</v>
+        <v>-1.279161304027298</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.007078</t>
+          <t>X ≈ 0.007062</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.352855333632242</v>
+        <v>2.489154714267009</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.138223506580026</v>
+        <v>-2.217737682524294</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.898011874151344</v>
+        <v>4.887710881844164</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.624590631499785</v>
+        <v>8.142457210502819</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.78935877410769</v>
+        <v>5.780461319008054</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.37944252775241</v>
+        <v>7.942902259581601</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.703669280084569</v>
+        <v>5.998199381462264</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.179721445087161</v>
+        <v>6.789498396265373</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.875501740263616</v>
+        <v>4.875082493777654</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.376935434273584</v>
+        <v>3.153302533398517</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.71471277161293</v>
+        <v>-0.8191250166870248</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.205906998320962</v>
+        <v>2.383695808728184</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.754613807245356</v>
+        <v>-1.785047023495991</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.230176858317556</v>
+        <v>-0.2781405262604935</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.008056</t>
+          <t>X ≈ 0.008044</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>113</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-6.453331853605874</v>
+        <v>-5.582957641556135</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.870175202889818</v>
+        <v>-1.850460985298511</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.270314509274847</v>
+        <v>0.4026955148153846</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.288562422044137</v>
+        <v>2.305686623421053</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.662414343201512</v>
+        <v>-1.713492924573394</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2753413557336728</v>
+        <v>1.182480145364316</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.076783767892458</v>
+        <v>1.124894102312368</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.489011237091866</v>
+        <v>1.538425806508613</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.222325910096224</v>
+        <v>-2.031354891814061</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.190455263098556</v>
+        <v>-1.973362971110603</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.374655791149813</v>
+        <v>-0.4128245769919161</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.28521339356471</v>
+        <v>1.415253664797724</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.296184951517944</v>
+        <v>5.444874499295793</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.406876353956889</v>
+        <v>6.578875113523551</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.009036</t>
+          <t>X ≈ 0.009025</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.702341397355475</v>
+        <v>3.644643773660505</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.694603580153682</v>
+        <v>8.608139803961024</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.6259002934251399</v>
+        <v>3.450742281033968</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.451419299516218</v>
+        <v>7.34088488800711</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1853049795586301</v>
+        <v>1.731582872563017</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.407424183776286</v>
+        <v>3.51941462187537</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4223668281969282</v>
+        <v>0.619020733562472</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.858625042655461</v>
+        <v>-0.8022702993523012</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.970789155370035</v>
+        <v>0.1081084453662982</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9284936814764961</v>
+        <v>1.178982572262164</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.092856518331359</v>
+        <v>0.02543922410360722</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.858847049558754</v>
+        <v>-3.725917848055246</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.9903403448587795</v>
+        <v>-0.3115519650952692</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.651397147462355</v>
+        <v>-1.014888055460851</v>
       </c>
     </row>
     <row r="32">
@@ -1924,49 +1924,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.37622682660853</v>
+        <v>0.3296912210307923</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.62218359068757</v>
+        <v>0.06908369959872829</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>-0.3819083823836564</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9.929065920949434</v>
+        <v>9.584228950941451</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>12.24791922499659</v>
+        <v>9.049176535055345</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.545293254631638</v>
+        <v>0.9571389690236742</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.746297181079797</v>
+        <v>6.484482421765506</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>10.56494282300734</v>
+        <v>6.047276708215989</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.789674952198915</v>
+        <v>3.204853509362053</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.511184727297568</v>
+        <v>0.9954758617887762</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.020769283323105</v>
+        <v>5.806794019543005</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.340861721392699</v>
+        <v>0.2311579400064545</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.77785372522218</v>
+        <v>2.652901421893326</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.7178750897343491</v>
+        <v>-2.731856532992715</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-16.88769569155132</v>
+        <v>-17.02624085714505</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-10.02430551342869</v>
+        <v>-8.931998587462196</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.944500626997318</v>
+        <v>-1.261220446744666</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.509190737646215</v>
+        <v>-4.357142857142883</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.732180726207247</v>
+        <v>3.218124130937483</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-2.055191006869507</v>
+        <v>-1.347800027662927</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.444986111898416</v>
+        <v>0.2044471089180391</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.996800518396995</v>
+        <v>-3.487192103078186</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.667952166445247</v>
+        <v>-1.911261486408556</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.907701471249652</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.722572121035299</v>
+        <v>-2.939230514759629</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.68819396867994</v>
+        <v>-2.881063777394736</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.108344821993349</v>
+        <v>-3.276221703958562</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.187693917529536</v>
+        <v>-1.41427361613674</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.050755019258993</v>
+        <v>3.049568232814337</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>20.51312649164685</v>
+        <v>20.51297310164253</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>17.0719230638066</v>
+        <v>17.0714285714286</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>16.53363351071085</v>
+        <v>16.58217943047662</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.54529325463163</v>
+        <v>2.569250663581244</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.110845676063043</v>
+        <v>-1.062833997072723</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.720771462706992</v>
+        <v>-8.671523900313275</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.488815272702418</v>
+        <v>-2.389467947407844</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.8779121404659733</v>
+        <v>0.9778201764846486</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.634996582365005</v>
+        <v>7.783686130142833</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.860732232591538</v>
+        <v>8.0327309921582</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1405 +2210,1405 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01592</t>
+          <t>X &gt; -0.01601</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4089</v>
+        <v>4101</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.07881093192298749</v>
+        <v>0.0907632358811199</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.06542043187609892</v>
+        <v>0.07641690080083663</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1472728331102005</v>
+        <v>0.1579147358837005</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1200532697801506</v>
+        <v>0.1308162768877921</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1075022968783514</v>
+        <v>0.1171116515402559</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1742203441396839</v>
+        <v>0.1842421456937231</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1517101275083661</v>
+        <v>0.1612583662601281</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1375923956569167</v>
+        <v>0.1470437020381539</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1633925877630986</v>
+        <v>0.1722355203321797</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1821211693065692</v>
+        <v>0.1657782680088715</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2111058284983471</v>
+        <v>0.2189786281693884</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2592889309467665</v>
+        <v>0.2665150988012925</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2441478223230789</v>
+        <v>0.2507753549112408</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3370624565373035</v>
+        <v>0.3429689132227409</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01495</t>
+          <t>X &gt; -0.01502</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4056</v>
+        <v>4069</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1118586069687169</v>
+        <v>0.1111522613452607</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1360198036387885</v>
+        <v>0.109112462169854</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.147992486237392</v>
+        <v>0.1208162388973548</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1194952653384362</v>
+        <v>0.09247714776030591</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1604126356449811</v>
+        <v>0.1315383599238515</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1760581590186305</v>
+        <v>0.1480025469689394</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1786659444847345</v>
+        <v>0.1498394923426503</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.06976099843112848</v>
+        <v>0.04100896559386769</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.09624968748572371</v>
+        <v>0.06666303890540348</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1220221657212122</v>
+        <v>0.09115356709531142</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1036186832456494</v>
+        <v>0.09724201201647986</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2011729232514625</v>
+        <v>0.1937929987005447</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1646631199191404</v>
+        <v>0.1564485029051923</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2564775129522019</v>
+        <v>0.2473853473876275</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01397</t>
+          <t>X &gt; -0.01404</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4016</v>
+        <v>4028</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1375997302003213</v>
+        <v>0.1501207908021982</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1531808952697489</v>
+        <v>0.1393843572839017</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1195332460545231</v>
+        <v>0.1056940721797162</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.08945198297482904</v>
+        <v>0.07574471096015856</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1112732622636656</v>
+        <v>0.09539645868004953</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1986587757904346</v>
+        <v>0.1835788527360407</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2021403684666083</v>
+        <v>0.1860596124156686</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.02221354830391675</v>
+        <v>0.006498622528326337</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.124168859187165</v>
+        <v>0.1071671227273754</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1835372503963555</v>
+        <v>0.165095544655621</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.09235780925348536</v>
+        <v>0.07410964737096037</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.190538177340926</v>
+        <v>0.1710454037467031</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1080575020278545</v>
+        <v>0.08769634182242925</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.148723126160121</v>
+        <v>0.1521805594727041</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01299</t>
+          <t>X &gt; -0.01306</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3970</v>
+        <v>3984</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.09252107717340152</v>
+        <v>0.07933025667418292</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1519963193952876</v>
+        <v>0.135940319186389</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.122521116112992</v>
+        <v>0.1062146535823771</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09058781613966715</v>
+        <v>0.07450461406395448</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.09375270792482127</v>
+        <v>0.07471994781055002</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1535673334939958</v>
+        <v>0.1358123583994981</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.08262391695392779</v>
+        <v>0.1139208441772155</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.0688599938940655</v>
+        <v>-0.03743868728064115</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.06011520377117563</v>
+        <v>0.06473702562858108</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1551562565232487</v>
+        <v>0.1825337720361873</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.09045394047313238</v>
+        <v>0.1178825219645674</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1641964933679532</v>
+        <v>0.1901694097279503</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.08562075044069672</v>
+        <v>0.08517385195676752</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1745141685397158</v>
+        <v>0.1978199192953198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01201</t>
+          <t>X &gt; -0.01208</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3914</v>
+        <v>3930</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1680905919822067</v>
+        <v>0.1281428681622288</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.4556685770387645</v>
+        <v>0.3968176348582233</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.3296402531146683</v>
+        <v>0.2706488184655953</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2050233987417656</v>
+        <v>0.2113850616388646</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2414373051830339</v>
+        <v>0.2691195530603352</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3233948063181344</v>
+        <v>0.3019648767424314</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2526913225160214</v>
+        <v>0.2298471597181404</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1822897617828545</v>
+        <v>0.1336445085137186</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3140434135410288</v>
+        <v>0.288599152194557</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4226555943580124</v>
+        <v>0.3685391700298553</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3344933432815012</v>
+        <v>0.3058503969633506</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4599336606893516</v>
+        <v>0.4292437079201363</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2841481970338577</v>
+        <v>0.2519784585216556</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.4222330720688632</v>
+        <v>0.3882380804897139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01103</t>
+          <t>X &gt; -0.0111</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3863</v>
+        <v>3876</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1642452597882311</v>
+        <v>0.1390651298455268</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3735664360301101</v>
+        <v>0.3820197319324663</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4059744131546523</v>
+        <v>0.3881982109812796</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2521819992940095</v>
+        <v>0.2491360929343429</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.2703513383377967</v>
+        <v>0.2630031113003284</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3236451016996185</v>
+        <v>0.318257578396647</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2272864760225843</v>
+        <v>0.2202313794770561</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1362606238418138</v>
+        <v>0.1549278550411586</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2963967722608913</v>
+        <v>0.286791891919286</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3917861532830003</v>
+        <v>0.3793096667305775</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2534202329942161</v>
+        <v>0.2670331547927205</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.4317876130947838</v>
+        <v>0.4428976926014414</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2851001020337378</v>
+        <v>0.29446397752114</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3961414260385183</v>
+        <v>0.3775636620682619</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01005</t>
+          <t>X &gt; -0.01012</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3800</v>
+        <v>3818</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1161458792243053</v>
+        <v>0.1145943647186556</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3817892434970673</v>
+        <v>0.3856873239608163</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.5000031320667233</v>
+        <v>0.4764004788629421</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.315267645733833</v>
+        <v>0.3070849975736252</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3426572514752309</v>
+        <v>0.3287256182146834</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.4707134226989069</v>
+        <v>0.4590732592862423</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.3479332649853788</v>
+        <v>0.3343566783606136</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2106150698356544</v>
+        <v>0.208482076973084</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2693070152737533</v>
+        <v>0.2906066630771562</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4066331274778321</v>
+        <v>0.3970312676627827</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2693700120710645</v>
+        <v>0.2599826619970074</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.4501275213476035</v>
+        <v>0.4376323887934177</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2027419125412706</v>
+        <v>0.188204889728361</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3381758416140812</v>
+        <v>0.321139283709492</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.009072</t>
+          <t>X &gt; -0.009134</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3722</v>
+        <v>3734</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.003016218051101305</v>
+        <v>-0.04015187829152467</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1147574691135063</v>
+        <v>0.1390208362855958</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3509715733942969</v>
+        <v>0.3473748110441761</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2399745245409548</v>
+        <v>0.2514598679439715</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4938020285201432</v>
+        <v>0.4983434375011555</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5378611587040112</v>
+        <v>0.5453456725552073</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4411163104482796</v>
+        <v>0.4459513352420004</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1766565720969879</v>
+        <v>0.19402231817417</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2110383445767354</v>
+        <v>0.2253284246423632</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2887494444595902</v>
+        <v>0.2991355838922942</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2451221117027629</v>
+        <v>0.2706065979839067</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4020862111886103</v>
+        <v>0.4241790215277064</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1314472174135375</v>
+        <v>0.09770410681140618</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2918368614393074</v>
+        <v>0.2815641086935088</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.008094</t>
+          <t>X &gt; -0.008153</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3626</v>
+        <v>3641</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.005668505781876831</v>
+        <v>0.00905575452156171</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2407727044623371</v>
+        <v>0.2878720976241951</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6039355175135981</v>
+        <v>0.5663831262932462</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5690533413441159</v>
+        <v>0.5195694716242585</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.8287825004113216</v>
+        <v>0.7578831457802551</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.9212910525947962</v>
+        <v>0.8814373803732707</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8243336820237843</v>
+        <v>0.7537275603717291</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.45517377079819</v>
+        <v>0.3701541912688882</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4646060816754272</v>
+        <v>0.430677536471137</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5669261751580521</v>
+        <v>0.5274436732074577</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4448924183858765</v>
+        <v>0.3936897076121042</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6051553109343573</v>
+        <v>0.5497314728864069</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.2833876178528101</v>
+        <v>0.225044881221514</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.4696676986698591</v>
+        <v>0.4072748772760946</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.007115</t>
+          <t>X &gt; -0.007171</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3528</v>
+        <v>3541</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.07774950523041468</v>
+        <v>-0.004481194256356957</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1216987813791874</v>
+        <v>0.101530909776983</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5343428990017998</v>
+        <v>0.5115650475731783</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3816826111898806</v>
+        <v>0.403420523138827</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.7486264385750943</v>
+        <v>0.7467328257992776</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7787801977960385</v>
+        <v>0.781523171231477</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8795712096269597</v>
+        <v>0.8492446206726427</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6547341189141491</v>
+        <v>0.6371474114592957</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5245942385200095</v>
+        <v>0.5030899864004326</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5686513400049691</v>
+        <v>0.5412191370168813</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5055932412348696</v>
+        <v>0.5223219501060328</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7666002887743204</v>
+        <v>0.765836516688104</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4759470742080936</v>
+        <v>0.4714331657159505</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6611857473307623</v>
+        <v>0.6518458507534319</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006136</t>
+          <t>X &gt; -0.00619</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3421</v>
+        <v>3433</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2304542318563136</v>
+        <v>0.1612006025230031</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2677695591081459</v>
+        <v>0.2330757821755185</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4139432944472503</v>
+        <v>0.4069609029784971</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2232816235665283</v>
+        <v>0.2622644641819463</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.822681685406657</v>
+        <v>0.8350959414576735</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.8445137306832038</v>
+        <v>0.8333702649101866</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.863551788702182</v>
+        <v>0.8469819793323623</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7046717072617739</v>
+        <v>0.7010096434910338</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4555628026661367</v>
+        <v>0.4766609741367844</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.439902226567213</v>
+        <v>0.4254869551234108</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2936293475941909</v>
+        <v>0.3250678066193302</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6201488963853876</v>
+        <v>0.632576641443606</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3042793743830288</v>
+        <v>0.3121826772765317</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4882012266200064</v>
+        <v>0.4903898494674976</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005157</t>
+          <t>X &gt; -0.005208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3309</v>
+        <v>3324</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1110068145530505</v>
+        <v>0.1135763310350626</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.203948524577882</v>
+        <v>0.2095596656693104</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4286874084139711</v>
+        <v>0.43198929840311</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.01608987407711737</v>
+        <v>0.03829668681153464</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.6237593077124259</v>
+        <v>0.6458048806567191</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.5155582837202388</v>
+        <v>0.5449765288298209</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4776533324721512</v>
+        <v>0.5008725666338236</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3592595838197283</v>
+        <v>0.3954001666108411</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.07349137731961974</v>
+        <v>0.1047464206448083</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.0859355578623493</v>
+        <v>0.108815019625105</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.002043822737157086</v>
+        <v>0.04175594014986928</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2780408213624952</v>
+        <v>0.3272849123032486</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.05623093713408878</v>
+        <v>0.09947560382703813</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.2991037734109412</v>
+        <v>0.3354643598735194</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004178</t>
+          <t>X &gt; -0.004226</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3179</v>
+        <v>3192</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.02849425804782868</v>
+        <v>0.003156985603183671</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.02871963222698781</v>
+        <v>0.01223715926717972</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.252611739606607</v>
+        <v>0.2600062059522656</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.08797290964872673</v>
+        <v>-0.06161021109475229</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4095190815117036</v>
+        <v>0.4661080019052193</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2532995340665281</v>
+        <v>0.3185473187860381</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3428513806490656</v>
+        <v>0.4001339293098169</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.01267936630193844</v>
+        <v>0.05937934278514234</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2448945009752492</v>
+        <v>-0.1792950259163533</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1344343502611594</v>
+        <v>-0.07854357765996411</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2762621982415681</v>
+        <v>-0.1712967472801878</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.08470077018677102</v>
+        <v>-0.03298168799322809</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2356233637266456</v>
+        <v>-0.2226670531599311</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.07077132844377587</v>
+        <v>0.04400918764692108</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.0032</t>
+          <t>X &gt; -0.003245</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3024</v>
+        <v>3038</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2721337551563821</v>
+        <v>0.2940862728499809</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.06357069962081141</v>
+        <v>0.08841000763508333</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5774616945501165</v>
+        <v>0.499849742062402</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1138234267231013</v>
+        <v>0.05703502273899375</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.7302682847128565</v>
+        <v>0.6690380741310875</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.5179476629296502</v>
+        <v>0.5002851463399125</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5174616389395368</v>
+        <v>0.523424685112353</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2997984561456732</v>
+        <v>0.3204040140851205</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3044776741638842</v>
+        <v>-0.2570153583303565</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2439847562261761</v>
+        <v>-0.208102304503754</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4486859144863686</v>
+        <v>-0.3939090479246445</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3151669822235803</v>
+        <v>-0.2516070711128933</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3531970421922566</v>
+        <v>-0.2993298995661888</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.1419132700539762</v>
+        <v>-0.06470152923746753</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.002221</t>
+          <t>X &gt; -0.002263</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2858</v>
+        <v>2872</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5361750053917049</v>
+        <v>0.5433232896168363</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1298099489768347</v>
+        <v>0.1051843723999113</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4171404532523582</v>
+        <v>0.4591723380187176</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.2332294711862843</v>
+        <v>0.2261904761904674</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8816763927851667</v>
+        <v>0.9021317948888949</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6747824804896183</v>
+        <v>0.6730926173189999</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5045926753166086</v>
+        <v>0.5273641259720989</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.09174725547215701</v>
+        <v>0.09628979450776853</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3344075364414891</v>
+        <v>-0.2882671038191589</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2210830049701684</v>
+        <v>-0.1889910946361582</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2509589884051877</v>
+        <v>-0.1650369663725186</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1816158010848312</v>
+        <v>-0.08738519073344975</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4072759404951469</v>
+        <v>-0.323817226229302</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1268714862928064</v>
+        <v>-0.05521170581236134</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.001242</t>
+          <t>X &gt; -0.001282</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2652</v>
+        <v>2668</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2812034734115301</v>
+        <v>0.365168234859091</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.005642237304073205</v>
+        <v>0.1262779308832194</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1953378493000315</v>
+        <v>0.2384120258113072</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4007792395976821</v>
+        <v>0.4634849455477195</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6522602769495265</v>
+        <v>0.7050098710640995</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5566874285540706</v>
+        <v>0.6619956149649937</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2669165692189495</v>
+        <v>0.3601257592203524</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1041621683868073</v>
+        <v>0.006526444403789355</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5963890779329688</v>
+        <v>-0.5167910955223931</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6344714251408021</v>
+        <v>-0.5342498122496124</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6507777077416179</v>
+        <v>-0.5304431812733057</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.5410416051225369</v>
+        <v>-0.4139863338765508</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.751735419142733</v>
+        <v>-0.6384088224879108</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5049217212977126</v>
+        <v>-0.4059068317869716</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.0002631</t>
+          <t>X &gt; -0.0003001</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2407</v>
+        <v>2425</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.03886305040190763</v>
+        <v>-0.06657999737158349</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.137650777842488</v>
+        <v>-0.1302498956691238</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2770038735854641</v>
+        <v>0.3609599545594691</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.407229017173826</v>
+        <v>0.4722858317186294</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.6560148576158369</v>
+        <v>0.6634764229578494</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.7691994768802104</v>
+        <v>0.7534194359853572</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.2513907608002413</v>
+        <v>0.2628567730624667</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4002761140075322</v>
+        <v>-0.3675850408188168</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6045159191704457</v>
+        <v>-0.6514712302025245</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3109702866382662</v>
+        <v>-0.4236383879183592</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1835834415775892</v>
+        <v>-0.27541587905786</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2737382904675911</v>
+        <v>-0.2766271305321482</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4214818229506108</v>
+        <v>-0.4838913047882727</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.2139309521672104</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0007157</t>
+          <t>X &gt; 0.0006815</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2148</v>
+        <v>2156</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2060785189280452</v>
+        <v>-0.2237376909377957</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1577817593558422</v>
+        <v>0.1792284109733302</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4132658321019562</v>
+        <v>0.3650987948032736</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.8221718860479612</v>
+        <v>0.7515025427646833</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.305712337596944</v>
+        <v>1.212812442238238</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.417299093660276</v>
+        <v>1.418989541085089</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.126275938381973</v>
+        <v>1.06018187594313</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5198020901342701</v>
+        <v>0.5017565229671916</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1661595433845946</v>
+        <v>-0.1833642343177502</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1723142954038721</v>
+        <v>0.1298862509643968</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2931945324925209</v>
+        <v>0.2761122458610288</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1415261732199298</v>
+        <v>0.1286420565741935</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.02680672661814043</v>
+        <v>-0.00852166206496463</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.04695598235925758</v>
+        <v>-0.08415212472492328</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.001695</t>
+          <t>X &gt; 0.001663</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1864</v>
+        <v>1878</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7696860840102886</v>
+        <v>-0.8407954496882581</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.071086747455858</v>
+        <v>1.020648556835809</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.264865389453092</v>
+        <v>1.239378191780311</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.234576889381742</v>
+        <v>1.186623721106471</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.712873746130882</v>
+        <v>1.682270422287388</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.849734132106263</v>
+        <v>1.878862984346028</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.474042668996589</v>
+        <v>1.423123191328656</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.7928412628972197</v>
+        <v>0.7978855425287321</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3333278713204422</v>
+        <v>0.3889681937532501</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7993488675517426</v>
+        <v>0.8174128910519229</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6482382773515596</v>
+        <v>0.6966651612870507</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2538918852267216</v>
+        <v>0.3593351994117384</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2968303038854785</v>
+        <v>-0.2187480703744384</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1481580187879956</v>
+        <v>-0.07619948098953699</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.002673</t>
+          <t>X &gt; 0.002645</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1595</v>
+        <v>1606</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1440839694656475</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.6921380264956269</v>
+        <v>0.6435531952203277</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.673226554185867</v>
+        <v>1.64680209792499</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.991068958562224</v>
+        <v>1.935479585510578</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.578482970194486</v>
+        <v>2.473707257488343</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.000309782818945</v>
+        <v>2.037194265603098</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.512969807577207</v>
+        <v>1.452693953237812</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.108479386568938</v>
+        <v>1.111084795338947</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6444025664756197</v>
+        <v>0.7014413787487399</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.8946433739141071</v>
+        <v>0.8445727167135999</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5646289324458991</v>
+        <v>0.6135699988016015</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.5990070848012223</v>
+        <v>0.6448410342157587</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4652697574657552</v>
+        <v>0.4718199141670141</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.440221708632734</v>
+        <v>0.4717987736917308</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.003652</t>
+          <t>X &gt; 0.003626</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.5960070463887277</v>
+        <v>0.6911076873081328</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.061744030247972</v>
+        <v>1.2420769436157</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.897741876262167</v>
+        <v>2.110989882725598</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.643351635235135</v>
+        <v>3.810796074154851</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.720446697524061</v>
+        <v>3.824349025587424</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.710128419466841</v>
+        <v>2.918748260785307</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.438587954201978</v>
+        <v>2.596035824765707</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.971519310415239</v>
+        <v>2.20671415849101</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.294678801313552</v>
+        <v>1.557652796485044</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.875041209798113</v>
+        <v>2.078919713935392</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.8228824244192765</v>
+        <v>0.999713991481876</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.319510191566586</v>
+        <v>1.48515431086966</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.9437310244841726</v>
+        <v>1.089996384305834</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.015264670084647</v>
+        <v>1.185667013192372</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.004631</t>
+          <t>X &gt; 0.004608</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1102547948015484</v>
+        <v>0.4254942357190714</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.186208816900859</v>
+        <v>1.304438362684436</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.902761808345439</v>
+        <v>2.994033707703068</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.432219197615183</v>
+        <v>5.453283683141493</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.893929644519488</v>
+        <v>5.020780677427034</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.655795036918484</v>
+        <v>3.830951925282548</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.858992547134093</v>
+        <v>3.960229359323954</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.199985323692836</v>
+        <v>3.304463075673745</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.891402399415739</v>
+        <v>2.032922565302393</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.633320036752764</v>
+        <v>2.784350629452533</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.371942605677965</v>
+        <v>1.494335060268774</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.214197799339722</v>
+        <v>1.362206840450028</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.65697460434302</v>
+        <v>0.7767539567025707</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.4980948699541656</v>
+        <v>0.5500614257588481</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.00561</t>
+          <t>X &gt; 0.005589</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4311037959836099</v>
+        <v>0.3662651640971006</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.793895398087066</v>
+        <v>1.720664578329256</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.753523022006128</v>
+        <v>3.530108964555552</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.370737013178143</v>
+        <v>5.12878125546424</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.956363197381087</v>
+        <v>4.834980550924826</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.518916904835258</v>
+        <v>3.708602109681202</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.301616706659544</v>
+        <v>4.384142339474153</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.586716588275529</v>
+        <v>3.672910806084673</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.28657705876639</v>
+        <v>2.408944331917198</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.880202805993058</v>
+        <v>1.901511343571428</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.427362689916485</v>
+        <v>1.276537449371631</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.089532405547246</v>
+        <v>1.088701726711925</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.7405866444767994</v>
+        <v>0.8165450301603983</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.5936514872499217</v>
+        <v>0.5735849721265609</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.006589</t>
+          <t>X &gt; 0.006571</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.424005461428656</v>
+        <v>-1.391900962267179</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.5420442178652394</v>
+        <v>0.6990433583277635</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.724508605467925</v>
+        <v>3.500193548926809</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.968554887267665</v>
+        <v>6.026243724326783</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.942460456123186</v>
+        <v>4.833608001905219</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.776419851611934</v>
+        <v>3.919983264313892</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.016912744378288</v>
+        <v>4.179839995601256</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.224640848559027</v>
+        <v>3.23323800444868</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.53764243187365</v>
+        <v>1.914214113260599</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.3625203835112671</v>
+        <v>0.7004196930415745</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.4830224772835976</v>
+        <v>0.7481463133702349</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.133005874426118</v>
+        <v>0.002454529834807317</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.6782725246637469</v>
+        <v>0.8934702367115008</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.9040081748902793</v>
+        <v>1.142515098726868</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.007567</t>
+          <t>X &gt; 0.007553</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.023215379775138</v>
+        <v>-2.724704099565095</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.439351238657785</v>
+        <v>1.700702506266168</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.996857511169559</v>
+        <v>3.023702715376359</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.079360312024725</v>
+        <v>5.299509503372157</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.324151019232723</v>
+        <v>4.508446711582636</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.235407912208373</v>
+        <v>2.538462486241386</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.452215991120077</v>
+        <v>3.55539260391248</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.900548648851775</v>
+        <v>2.011973636632582</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.7549677938474488</v>
+        <v>0.8974148205992307</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3118707421787335</v>
+        <v>-0.1419310015950543</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.218786017131578</v>
+        <v>1.286366921316464</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9160332274762197</v>
+        <v>-0.8152935551415368</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.827543166215925</v>
+        <v>1.813306617646681</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.618496207746809</v>
+        <v>1.63038603689747</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.008546</t>
+          <t>X &gt; 0.008534</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.906203386856184</v>
+        <v>-1.801896527436561</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.517093278700671</v>
+        <v>2.847221004971324</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.559103503141031</v>
+        <v>3.869913611557472</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.988179221442039</v>
+        <v>6.26608660461352</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.59931495570266</v>
+        <v>6.517244365541586</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.873700479590624</v>
+        <v>2.976251070581696</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.225771729519856</v>
+        <v>4.340096405857665</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.034565154698647</v>
+        <v>2.164861936072604</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.398870354497703</v>
+        <v>1.842989042035526</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.02576108551032519</v>
+        <v>0.4493598914199737</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.493675687263973</v>
+        <v>1.834963033627467</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.632865700610587</v>
+        <v>-1.535441657579064</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.6979854666795262</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.05916780278502642</v>
+        <v>0.03273099215819286</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.009525</t>
+          <t>X &gt; 0.009516</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.933198188210703</v>
+        <v>-4.136128085049585</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.6796821087669684</v>
+        <v>0.378255805404315</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.849226076709023</v>
+        <v>4.049558467496112</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.224264498305679</v>
+        <v>5.805458768873407</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.420414779234882</v>
+        <v>8.568242148246682</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.078784659492371</v>
+        <v>2.743466691455851</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.898638615578903</v>
+        <v>5.934843122555598</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.18675669378387</v>
+        <v>3.436490036968998</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.8809612592528</v>
+        <v>2.586509297750908</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3712914255785336</v>
+        <v>0.1366644567733246</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.071154582671042</v>
+        <v>2.610473237709115</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2139693396624338</v>
+        <v>-0.5966661473749824</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.440568603704662</v>
+        <v>1.048992252591809</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.251366494595082</v>
+        <v>0.4817105839949321</v>
       </c>
     </row>
     <row r="33">
@@ -3618,49 +3618,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-5.697290299540207</v>
+        <v>-5.958387686955952</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2938627886825245</v>
+        <v>0.5044122393824537</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.74704462030175</v>
+        <v>5.857800687849355</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.707679120615261</v>
+        <v>4.263546798029545</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.26295681898155</v>
+        <v>8.371998806502923</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.472370532218399</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.551643881163336</v>
+        <v>5.710565017705584</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.575803307552036</v>
+        <v>2.371169038931434</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.099616472666682</v>
+        <v>2.334196429794638</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>-0.2137700820548218</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.04499651807663</v>
+        <v>1.306227401443564</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.25980661611775</v>
+        <v>-0.9344564359041883</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.07442849548112207</v>
+        <v>0.394523568566477</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.469754788982513</v>
+        <v>1.79299371793816</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>112</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1976553980370781</v>
+        <v>0.1684596036844468</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.729326447830388</v>
+        <v>5.728139661385732</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.036208778092281</v>
+        <v>9.035714285714278</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.17649065356802</v>
+        <v>11.22503657333379</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.116721826060243</v>
+        <v>6.140679235009856</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.710582895365505</v>
+        <v>8.758594574355826</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.564942823007335</v>
+        <v>5.614190385401052</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.61110352362742</v>
+        <v>4.684360633407117</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.868327584440422</v>
+        <v>2.967674909734995</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>3.556483569037368</v>
+        <v>3.656391605056044</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.01943314996412226</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.277853725222144</v>
+        <v>2.426543272999972</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.396446518305815</v>
+        <v>3.568445277872478</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>6.622183590687527</v>
+        <v>6.620996804242871</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.227412205932488</v>
+        <v>6.227258815928167</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6.35763734952085</v>
+        <v>6.357142857142847</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>9.390776367853739</v>
+        <v>9.439322287619511</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.307198016536439</v>
+        <v>7.331155425486052</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.32684758491211</v>
+        <v>10.37609514730583</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>4.753389195449273</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.449340711894507</v>
+        <v>4.549248747913182</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2781858976549216</v>
+        <v>-0.154489276626677</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.908351280210582</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1405 +3904,1405 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01592</t>
+          <t>X &lt; -0.01601</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.861868411486739</v>
+        <v>-5.522160017658067</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-2.286059994380189</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-8.058302079781789</v>
+        <v>-8.703894368237059</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.547124555241048</v>
+        <v>-6.164371772805509</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-5.448801636649002</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.978516269177852</v>
+        <v>-7.585654672046935</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-5.236672207055534</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.958866700802183</v>
+        <v>-4.497685690330442</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4.019848857324959</v>
+        <v>-4.534658299467239</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.869767653654819</v>
+        <v>-4.153667603173787</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.767446604926747</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.611519230988264</v>
+        <v>-9.118918421778716</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.841193893825476</v>
+        <v>-8.309257071234107</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-12.37736300550371</v>
+        <v>-12.87948931765248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01495</t>
+          <t>X &lt; -0.01502</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.617668167286489</v>
+        <v>-4.684024868365242</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-3.664751696247755</v>
+        <v>-2.788941083955876</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.768924790404505</v>
+        <v>-4.92180950705319</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.929297937414432</v>
+        <v>-3.052795031055901</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-5.322288345210978</v>
+        <v>-4.411609389399132</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.024914315575892</v>
+        <v>-4.138823870580204</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.254923820141208</v>
+        <v>-3.329914742414353</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4484881904236673</v>
+        <v>0.5520785841588207</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5094703469464434</v>
+        <v>0.5151059750220242</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.359389143276303</v>
+        <v>-0.3087226057929584</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-0.512863053329049</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.093814713283734</v>
+        <v>-3.932957185529375</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.80456385719544</v>
+        <v>-2.588984677310592</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.997631625772328</v>
+        <v>-5.818200684860443</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01397</t>
+          <t>X &lt; -0.01404</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.073272718432442</v>
+        <v>-4.433188747963904</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.136688110859325</v>
+        <v>-2.811237627991559</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.531459495614364</v>
+        <v>-3.204975616306264</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.127349001707536</v>
+        <v>-1.793040293040292</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.66563855480323</v>
+        <v>-2.282289433992212</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.279092550645849</v>
+        <v>-3.932580838250217</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.726860234752778</v>
+        <v>-3.352211286450036</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.9016125227343679</v>
+        <v>1.310161081371753</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.070197659266121</v>
+        <v>-0.6498884508419707</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.557059130755214</v>
+        <v>-2.114742672682588</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2139895883784604</v>
+        <v>0.2452194438838831</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.727382136660083</v>
+        <v>-2.260716382853786</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.599762289336546</v>
+        <v>-0.09177174531505017</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.647911989428486</v>
+        <v>-1.76580380637661</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01299</t>
+          <t>X &lt; -0.01306</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.234610611815135</v>
+        <v>-2.010111824886984</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.367964192563697</v>
+        <v>-2.093288910042837</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.762735577318736</v>
+        <v>-2.487026898357541</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.647288758853527</v>
+        <v>-1.357142857142861</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.692967474510795</v>
+        <v>-1.346391998094781</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.380815119752555</v>
+        <v>-2.073606479275853</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.4950821292650289</v>
+        <v>-1.134262568501313</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.486125089017193</v>
+        <v>1.899904671115337</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.454699582740723</v>
+        <v>0.3629320619785545</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.380440888465984</v>
+        <v>-1.960896518836435</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1073095344109092</v>
+        <v>-0.6650369663725186</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.550763894370853</v>
+        <v>-2.106870229007633</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.0004713979305677185</v>
+        <v>-0.002028155571466073</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.745179097457729</v>
+        <v>-2.252983293556092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01201</t>
+          <t>X &lt; -0.01208</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.865531415149739</v>
+        <v>-2.314033393514435</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.399794431290488</v>
+        <v>-5.66809205964914</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.256104277583987</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.005297013413511</v>
+        <v>-3.176040494938135</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.543586566509205</v>
+        <v>-4.058990423291633</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.404513695175275</v>
+        <v>-4.179905691874282</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.944822510039899</v>
+        <v>-2.665758631493446</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.867489609425085</v>
+        <v>-1.163087454868901</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.472873310349414</v>
+        <v>-3.168564001013586</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.094992878880042</v>
+        <v>-4.386093369230139</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.755292492738697</v>
+        <v>-3.409131454561503</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.651416270885299</v>
+        <v>-5.319468654204485</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.982764035395618</v>
+        <v>-2.565020281555704</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-5.073630701771407</v>
+        <v>-4.678180143949795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01103</t>
+          <t>X &lt; -0.0111</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.320144326354288</v>
+        <v>-2.024674931683101</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.252873827778245</v>
+        <v>-4.417964234718156</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.29073202925354</v>
+        <v>-5.136377547708193</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.066325784119691</v>
+        <v>-3.058441558441565</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.282034692054104</v>
+        <v>-3.223015374718152</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.629821952741601</v>
+        <v>-3.599580505249882</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.101629086201314</v>
+        <v>-2.036859971098714</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.9557945041815898</v>
+        <v>-1.203991432780761</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.629679886510829</v>
+        <v>-2.539665340618853</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.802179328001976</v>
+        <v>-3.688169246109162</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.071396615294418</v>
+        <v>-2.268933070268631</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.295082979068134</v>
+        <v>-4.483493605631004</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.457169316252504</v>
+        <v>-2.605924259467564</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.844336891832434</v>
+        <v>-3.655580696153493</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01005</t>
+          <t>X &lt; -0.01012</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.411397313956805</v>
+        <v>-1.423155303147851</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.557342765309407</v>
+        <v>-3.68456956399379</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.28901254578637</v>
+        <v>-5.168225808439281</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.150214048410973</v>
+        <v>-3.130984818995721</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.420407086761358</v>
+        <v>-3.34775439591494</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.463515630852811</v>
+        <v>-4.437366697259506</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.93964690164713</v>
+        <v>-2.863145402288779</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.53003994221671</v>
+        <v>-1.548182760578641</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.859118613484796</v>
+        <v>-2.131603457147129</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.245230439305267</v>
+        <v>-3.228656081677961</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.84135250909361</v>
+        <v>-1.793452266918969</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.683649959955446</v>
+        <v>-3.647853835565009</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.154739151070466</v>
+        <v>-1.037547281254525</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.537582589315782</v>
+        <v>-2.427846681534227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.009072</t>
+          <t>X &lt; -0.009134</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1630352358323677</v>
+        <v>0.1447554317501911</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.6704685695142985</v>
+        <v>-0.8782113047213329</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.051994921156755</v>
+        <v>-3.045785213213421</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.923020046180788</v>
+        <v>-2.028983211910045</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.009982165648161</v>
+        <v>-4.070338783017171</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.15508601211927</v>
+        <v>-4.241012244242597</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.133601681119956</v>
+        <v>-3.193020883357192</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.9458030682695195</v>
+        <v>-1.100095328884656</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.006785224792296</v>
+        <v>-1.137067938021453</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.635465083069064</v>
+        <v>-1.738674296614207</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.276031476892307</v>
+        <v>-1.498370299705861</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.572030264670019</v>
+        <v>-2.773536895674297</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3314272377173566</v>
+        <v>-0.0575837111270161</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.65779801764603</v>
+        <v>-1.586316626889428</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.008094</t>
+          <t>X &lt; -0.008153</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1172796668979856</v>
+        <v>-0.2165338432356094</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.364829396325462</v>
+        <v>-1.703583027689895</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.123237144716853</v>
+        <v>-3.935556310122251</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.71912559609455</v>
+        <v>-3.438025210084042</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.44238317333501</v>
+        <v>-5.030215527506542</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-5.87493615099919</v>
+        <v>-5.67654765574644</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.047237751141267</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.594598365730924</v>
+        <v>-2.061421295735485</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.473098770428884</v>
+        <v>-2.282555967487383</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.140535814933934</v>
+        <v>-2.922222485687264</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.334414837857381</v>
+        <v>-2.021390557532754</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.396928824441723</v>
+        <v>-3.068196195858462</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.2576646868959</v>
+        <v>-0.8850852458108704</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.494451888588934</v>
+        <v>-2.109336884716321</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.007115</t>
+          <t>X &lt; -0.007171</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5548759689010723</v>
+        <v>-0.1070110496931846</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4711468077276137</v>
+        <v>-0.3665808355086781</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.023083061511926</v>
+        <v>-2.934231867301641</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.041833549950042</v>
+        <v>-2.183229813664603</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.044860638107849</v>
+        <v>-4.069994482566834</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.056605619291922</v>
+        <v>-4.107767969959077</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.450434989377257</v>
+        <v>-4.323703562290135</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.217349073658589</v>
+        <v>-3.156082887205024</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.350974197723872</v>
+        <v>-2.259929524335611</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.582654972415398</v>
+        <v>-2.461674123813111</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.240177200533616</v>
+        <v>-2.354772580680461</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.672427315152156</v>
+        <v>-3.696294801324896</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.077074292496576</v>
+        <v>-2.069679788541912</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.091648719789418</v>
+        <v>-3.064802889201502</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006136</t>
+          <t>X &lt; -0.00619</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.15816470778303</v>
+        <v>-0.8500852644620167</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.049774081270137</v>
+        <v>-0.901799548340712</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.973645995125707</v>
+        <v>-1.960431153676694</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.9791649210562525</v>
+        <v>-1.165653495440736</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.701303965605909</v>
+        <v>-3.782562210860739</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.669181925360746</v>
+        <v>-3.642755415446068</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.621266289931953</v>
+        <v>-3.570432781267272</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.894700981464048</v>
+        <v>-2.90302475631475</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.629423191037219</v>
+        <v>-1.741595234958865</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.550960024502359</v>
+        <v>-1.50017747755814</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.8864589466143116</v>
+        <v>-1.038538963709414</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.374183871312475</v>
+        <v>-2.44508594139112</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.9326325969663145</v>
+        <v>-0.9760627760774483</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.770726733973817</v>
+        <v>-1.792264252277796</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005157</t>
+          <t>X &lt; -0.005208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5223906849122315</v>
+        <v>-0.537954052265178</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.6358809254414979</v>
+        <v>-0.667040361843064</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.721896549827875</v>
+        <v>-1.757642461656033</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.03138884919392382</v>
+        <v>-0.1178861788617951</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.354522213472563</v>
+        <v>-2.465439617142394</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.82620130162038</v>
+        <v>-1.960366061157387</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.564491337560924</v>
+        <v>-1.672590094633719</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.107772452479296</v>
+        <v>-1.262886026559073</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1014532431919264</v>
+        <v>-0.02078886825401582</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.059848534621878</v>
+        <v>-0.03066396069689858</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3824538415394372</v>
+        <v>0.2303118708367791</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.6750112944803206</v>
+        <v>-0.8743120894727525</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1779860003544229</v>
+        <v>0.00959975140528968</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7536857568264637</v>
+        <v>-0.9041460842537674</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004178</t>
+          <t>X &lt; -0.004226</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1763068120974793</v>
+        <v>-0.09562490335780183</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.216515110870759</v>
+        <v>0.08596587344155182</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.8796590794955037</v>
+        <v>-0.9120017221239038</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3073436111629277</v>
+        <v>0.224931664508695</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.280480086535249</v>
+        <v>-1.472776690944734</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6819012376230518</v>
+        <v>-0.8978763685004196</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.8670132033149258</v>
+        <v>-1.059237392267676</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.272343855709579</v>
+        <v>0.04103370337340806</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.114976157018127</v>
+        <v>0.9113191587527325</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7670653928167752</v>
+        <v>0.5915228360022766</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.222492183538442</v>
+        <v>0.8914146465306985</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6104794276301178</v>
+        <v>0.4455491258310786</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.095761169890153</v>
+        <v>1.058455715396278</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.114253359352098</v>
+        <v>0.1986296096697231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.0032</t>
+          <t>X &lt; -0.003245</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7896757876896032</v>
+        <v>-0.8550595600786153</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.05914462142992249</v>
+        <v>-0.1264188141404858</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.581409501414804</v>
+        <v>-1.391996383972185</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.2767872536537439</v>
+        <v>-0.128720886785409</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.897544347052559</v>
+        <v>-1.751361483709424</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.252646425149877</v>
+        <v>-1.217024090435395</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.163594838282251</v>
+        <v>-1.190496221509164</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5880918052662096</v>
+        <v>-0.6498335487799451</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.088545499548985</v>
+        <v>0.9711345052595206</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.9336744877543097</v>
+        <v>0.8453862036766537</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.474185432391401</v>
+        <v>1.339326035372672</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.123654211756985</v>
+        <v>0.9611925982174938</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.225696569931834</v>
+        <v>1.089594881077758</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6681424029259873</v>
+        <v>0.4660393940529843</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.002221</t>
+          <t>X &lt; -0.002263</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.229968342892199</v>
+        <v>-1.255358973175959</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1876290379272163</v>
+        <v>-0.1359068704690145</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.9614754795435161</v>
+        <v>-1.062369364110964</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4871491234902052</v>
+        <v>-0.4758643183300819</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.895697219303223</v>
+        <v>-1.954458969175448</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.370532756866318</v>
+        <v>-1.377259447312376</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9237321062615607</v>
+        <v>-0.9812945319716349</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.02405815323736959</v>
+        <v>-0.03535808592959455</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9779817099816839</v>
+        <v>0.8842735253931764</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.7355040677900249</v>
+        <v>0.6702010421391691</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8019242985206461</v>
+        <v>0.6184996189933329</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6515624275306635</v>
+        <v>0.4480078197728545</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.143959102734357</v>
+        <v>0.9674840395504916</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.5331928518202176</v>
+        <v>0.3781142674195124</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.001242</t>
+          <t>X &lt; -0.001282</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5464898010261479</v>
+        <v>-0.6997102449001531</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.07183230263132856</v>
+        <v>-0.1407197400823605</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3885128526155128</v>
+        <v>-0.4685815755643929</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6821076823501642</v>
+        <v>-0.7998306041784318</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.11949471365832</v>
+        <v>-1.223203592297672</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.887780565835449</v>
+        <v>-1.082170379144102</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3158921069794829</v>
+        <v>-0.4840649400428134</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3332572400413838</v>
+        <v>0.1405111312339997</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.257173310701802</v>
+        <v>1.129422827150051</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.32649285974292</v>
+        <v>1.163114035253273</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.356605588935999</v>
+        <v>1.156862769775223</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.165882854106137</v>
+        <v>0.9511772643960654</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.534686635901203</v>
+        <v>1.347576066064427</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.102960090204007</v>
+        <v>0.936990321219632</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.0002631</t>
+          <t>X &lt; -0.0003001</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1766</v>
+        <v>1759</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.004959675680339615</v>
+        <v>0.04380417965330707</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2581803622775283</v>
+        <v>0.2508337475380813</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4190768981837252</v>
+        <v>-0.540405660424554</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5409332714918307</v>
+        <v>-0.6376652875801128</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8791008137881562</v>
+        <v>-0.8997707601617932</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.9776543859630209</v>
+        <v>-0.9677007438982272</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2139484556364337</v>
+        <v>-0.2333539938278335</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.676448963925246</v>
+        <v>0.6385410347517038</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.011394409212429</v>
+        <v>1.08805997556582</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6139643006653728</v>
+        <v>0.7758857438128004</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4413368312251009</v>
+        <v>0.5717452962767098</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.56445013750659</v>
+        <v>0.5730615504124899</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.767175841384578</v>
+        <v>0.860109422597958</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4832852175454221</v>
+        <v>0.5406494523222491</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0007157</t>
+          <t>X &lt; 0.0006815</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.17656428442627</v>
+        <v>0.1965810884988386</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1058816511572331</v>
+        <v>-0.1297241636125079</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.4740719327746916</v>
+        <v>-0.4249884936308135</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.8591114189520539</v>
+        <v>-0.7874727438981566</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.371034517170557</v>
+        <v>-1.276721884850076</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.441745347791539</v>
+        <v>-1.447067828364972</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.082668724809189</v>
+        <v>-1.015355626108402</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4379467393296821</v>
+        <v>-0.4202923732196311</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.3397489531855342</v>
+        <v>0.3582499525650391</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.01682993194551585</v>
+        <v>0.02727499422419299</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1445106489854737</v>
+        <v>-0.1275800910644946</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.01634673021104049</v>
+        <v>0.0291573707952324</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1394057534408333</v>
+        <v>0.1761384289529317</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2169932555192275</v>
+        <v>0.255892446088879</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.001695</t>
+          <t>X &lt; 0.001663</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.584714366702265</v>
+        <v>0.6500613352861819</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8105822617674434</v>
+        <v>-0.7801663461623676</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.052748238374818</v>
+        <v>-1.043977959422939</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.9858618479109253</v>
+        <v>-0.9574027098929676</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.371375444881735</v>
+        <v>-1.360034267475463</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.440124441858686</v>
+        <v>-1.47702787381894</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.092308849567758</v>
+        <v>-1.061287254512578</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5409482569209558</v>
+        <v>-0.5507019146732191</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1259459911157279</v>
+        <v>-0.1739123246707877</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.4998803651175905</v>
+        <v>-0.520931195906229</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3774991149453157</v>
+        <v>-0.4216472828007838</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.0590640349644147</v>
+        <v>-0.1467488592633828</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.386960945416412</v>
+        <v>0.3250199588628746</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.2662262621652474</v>
+        <v>0.2084217367995009</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.002673</t>
+          <t>X &lt; 0.002645</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2578</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1220606554376857</v>
+        <v>-0.1088724755453825</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3798051398394833</v>
+        <v>-0.354428003417496</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.0632758294364</v>
+        <v>-1.058123372592341</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.221973442164234</v>
+        <v>-1.199452039630266</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.58483338824383</v>
+        <v>-1.533722490152122</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.189353198837395</v>
+        <v>-1.22219229872568</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.8480372219300492</v>
+        <v>-0.8179123166609372</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5968438598951877</v>
+        <v>-0.6039712978769032</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2703792903427953</v>
+        <v>-0.3096154370520878</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4228939797373599</v>
+        <v>-0.3967243590845868</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.2184333744842206</v>
+        <v>-0.2518923366710837</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2398727825678719</v>
+        <v>-0.271275037072769</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1559522903985311</v>
+        <v>-0.1623616181538594</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1410410135571993</v>
+        <v>-0.1629910515079871</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.003652</t>
+          <t>X &lt; 0.003626</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2876</v>
+        <v>2880</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2979638475821744</v>
+        <v>-0.3437340085958169</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4352563696986991</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8807708731243693</v>
+        <v>-0.9849464545295277</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.633790230876549</v>
+        <v>-1.721914008321782</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.66801217185084</v>
+        <v>-1.725726256069819</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.178612135361881</v>
+        <v>-1.279570418249499</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.020351304069209</v>
+        <v>-1.097508060873018</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.8090651135005942</v>
+        <v>-0.9204213781389043</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4690954541922636</v>
+        <v>-0.5916133925669129</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7285314439920754</v>
+        <v>-0.8255738262618308</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.25382616986861</v>
+        <v>-0.3357517477743386</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.4780468639392481</v>
+        <v>-0.5551700208188706</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.3073044256294395</v>
+        <v>-0.3756831364808662</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.3401419974899298</v>
+        <v>-0.4196499602227561</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.004631</t>
+          <t>X &lt; 0.004608</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3133</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.0636132315521607</v>
+        <v>-0.170092722690228</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3536356902542437</v>
+        <v>-0.3990213941192735</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9859187024970808</v>
+        <v>-1.030512084722631</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.793770300454135</v>
+        <v>-1.824489145769817</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.614683140790483</v>
+        <v>-1.676592698954927</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.172906353978888</v>
+        <v>-1.244520783194297</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.208724215624201</v>
+        <v>-1.256314831088943</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9893173892063345</v>
+        <v>-1.035702596975185</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5228250478011489</v>
+        <v>-0.5771189584296224</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.7668764971922357</v>
+        <v>-0.8269679474078657</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3478796116416021</v>
+        <v>-0.3933532929031429</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2956593835393946</v>
+        <v>-0.3492944714318682</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.1095562483397146</v>
+        <v>-0.1523153285133887</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.05728336177261184</v>
+        <v>-0.07679433728414864</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.00561</t>
+          <t>X &lt; 0.005589</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3368</v>
+        <v>3371</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1281489396790718</v>
+        <v>-0.1136621207449693</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3916876771801796</v>
+        <v>-0.3791723074976971</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.918617659967083</v>
+        <v>-0.8754223986535692</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.27607964438571</v>
+        <v>-1.233068234696901</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.176419399342031</v>
+        <v>-1.159687822791255</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.8038472314382688</v>
+        <v>-0.8572902222429803</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.9615508558521455</v>
+        <v>-0.9908976395913598</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7899122862961647</v>
+        <v>-0.8186138474031708</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4491265903701205</v>
+        <v>-0.4838373511809095</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3497721740034478</v>
+        <v>-0.3592367677990893</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.2412061299876385</v>
+        <v>-0.2077162787613815</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1605163899587083</v>
+        <v>-0.1626069618863824</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.07606647152975654</v>
+        <v>-0.096334205393525</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.04137160181634414</v>
+        <v>-0.03821022918349826</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.006589</t>
+          <t>X &lt; 0.006571</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3559</v>
+        <v>3562</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2214082483791202</v>
+        <v>0.2202158144297357</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.05848867822003001</v>
+        <v>-0.08768666914647838</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6622727798578438</v>
+        <v>-0.6344071169061607</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.02144657104288</v>
+        <v>-1.049967969250488</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.8439146490071678</v>
+        <v>-0.8385444644624869</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6155111680908547</v>
+        <v>-0.6498396631323615</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.6289783148128123</v>
+        <v>-0.6673435889666877</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4916549002570534</v>
+        <v>-0.5011048633770869</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1724356287722415</v>
+        <v>-0.24225727883492</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.03183925525136289</v>
+        <v>-0.02821769695705711</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.01138187208226071</v>
+        <v>-0.03600470830801328</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1177477567057039</v>
+        <v>0.0940276385569021</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.0215042202032194</v>
+        <v>-0.06082692065706397</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.06083482075410984</v>
+        <v>-0.1047519628430109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.007567</t>
+          <t>X &lt; 0.007553</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3713</v>
+        <v>3721</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.3512987345663205</v>
+        <v>0.3175483198463311</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1447337025455511</v>
+        <v>-0.1790797947613427</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3907144968033904</v>
+        <v>-0.3974586494972527</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6220970482683512</v>
+        <v>-0.6554261189454351</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5278323010908679</v>
+        <v>-0.5545465045325528</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2427251785480422</v>
+        <v>-0.2817609857136247</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3665979904332772</v>
+        <v>-0.3815123672670779</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.173549453946471</v>
+        <v>-0.1886621565819198</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.004513909786624026</v>
+        <v>-0.02297397828990455</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1292071784739477</v>
+        <v>0.107846767951969</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.06036895932255959</v>
+        <v>-0.06944083318240502</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2045435430712814</v>
+        <v>0.1918136280968454</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.1348318659771834</v>
+        <v>-0.1344838245666224</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1093343289105277</v>
+        <v>-0.1121609339753391</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.008546</t>
+          <t>X &lt; 0.008534</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3826</v>
+        <v>3834</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.1433741272462115</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.195828993548659</v>
+        <v>-0.2291202917758568</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3419308597609358</v>
+        <v>-0.3745854616058537</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5365701379069634</v>
+        <v>-0.5690668352735599</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.5913385438386456</v>
+        <v>-0.5896880147571082</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2276186755982863</v>
+        <v>-0.2387978356934539</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3242366692035361</v>
+        <v>-0.3373875685013132</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1245451883287458</v>
+        <v>-0.137865581554621</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.04061225406746871</v>
+        <v>-0.08235194010587321</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.0901870777807261</v>
+        <v>0.04640084889877727</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.04759912987291415</v>
+        <v>-0.07955351576006819</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2366398392768971</v>
+        <v>0.2278534414824591</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.02553001026450374</v>
+        <v>0.02991447806608249</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.08312040375126628</v>
+        <v>0.08504487545799577</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.009525</t>
+          <t>X &lt; 0.009516</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3932</v>
+        <v>3939</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2187037413287598</v>
+        <v>0.2360283927794313</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.009952022178303821</v>
+        <v>0.007976912741966657</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3149232166971174</v>
+        <v>-0.2707696180334125</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3738984916040309</v>
+        <v>-0.3551165146909909</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.568624799362702</v>
+        <v>-0.5266554893539706</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1559395227432319</v>
+        <v>-0.1387357240807248</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3029901652372615</v>
+        <v>-0.312336079274445</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1975907328223059</v>
+        <v>-0.1558762619475402</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.0922148115806749</v>
+        <v>-0.07746864814065191</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.06272363554379012</v>
+        <v>0.07664787487235003</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1023020544877724</v>
+        <v>-0.07675690548972369</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.09886883883041264</v>
+        <v>0.1225131762194636</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.001849155167235494</v>
+        <v>0.0208144840224449</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.009402484008475653</v>
+        <v>0.05572450030021514</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4002</v>
+        <v>4010</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2214500964893062</v>
+        <v>0.2365946130946242</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01851073140930026</v>
+        <v>0.009147688664278064</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2631007697536702</v>
+        <v>-0.2716575872409095</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1941359021526878</v>
+        <v>-0.1780383795309248</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3449503835798211</v>
+        <v>-0.3552250411403222</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1087858333626244</v>
+        <v>-0.1186537664834191</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1799045792451892</v>
+        <v>-0.1906479307119184</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.009622332396141076</v>
+        <v>-0.04531445239063459</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.006930987406839506</v>
+        <v>-0.01876158683838725</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.105507528809575</v>
+        <v>0.09291514035638215</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.03967422357634121</v>
+        <v>0.02733781558610815</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1380645185954918</v>
+        <v>0.124435852747105</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.08173295865421437</v>
+        <v>0.06740590077358632</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.02179455857139345</v>
+        <v>0.006368327391534478</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4061</v>
+        <v>4072</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.02632594707828417</v>
+        <v>-0.02541170248796476</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1269658604015262</v>
+        <v>-0.1265895956451857</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2874628993158979</v>
+        <v>-0.2866840132240611</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.242180175130855</v>
+        <v>-0.2415132638062616</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3003433232659631</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1370084692035931</v>
+        <v>-0.137331969471937</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1837491737453192</v>
+        <v>-0.1846425635981461</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.09647837197667997</v>
+        <v>-0.09764314644228023</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.04554393614350261</v>
+        <v>-0.04754132531603261</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.00371679547538406</v>
+        <v>0.0008306646768119208</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>-0.01779770256884206</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.08250231068279845</v>
+        <v>0.07869678130164459</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.02087264623220619</v>
+        <v>0.01650854955989445</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.01030586499174291</v>
+        <v>-0.01526227194509744</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4089</v>
+        <v>4100</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.06745918021743336</v>
+        <v>-0.06663990657917651</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1052696437152321</v>
+        <v>-0.1049620617938132</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1454100937190717</v>
+        <v>-0.1450176548644677</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1239086721569009</v>
+        <v>-0.1235662148070915</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.185323471789296</v>
+        <v>-0.1858906595695871</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1186768977446278</v>
+        <v>-0.1188839865786804</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1900867474916339</v>
+        <v>-0.1906297464901101</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1554478973833753</v>
+        <v>-0.1561109158305882</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.0808673047625561</v>
+        <v>-0.08225673217491902</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.01333448669147685</v>
+        <v>-0.01547741552258941</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.008835520475258818</v>
+        <v>-0.01100333244613694</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.08818162222029713</v>
+        <v>0.08523118493678083</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.07299867806879945</v>
+        <v>0.0695397546943255</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.04359217040378383</v>
+        <v>0.03969963327317316</v>
       </c>
     </row>
   </sheetData>
